--- a/research/traditional_assets/database/data/denmark/denmark_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_healthcare_support_services.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08148062653468752</v>
+        <v>0.08133646915631121</v>
       </c>
       <c r="C2">
-        <v>27.34141678764545</v>
+        <v>27.15897725450182</v>
       </c>
       <c r="D2">
-        <v>25.70141678764545</v>
+        <v>25.80567725450182</v>
       </c>
       <c r="E2">
-        <v>-5.87</v>
+        <v>-5.5833</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
       <c r="G2">
         <v>1.64</v>
@@ -1433,28 +1433,28 @@
         <v>2.835</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01442101</v>
       </c>
       <c r="N2">
-        <v>2.835</v>
+        <v>2.82057899</v>
       </c>
       <c r="O2">
-        <v>0.6237</v>
+        <v>0.6205273778</v>
       </c>
       <c r="P2">
-        <v>2.2113</v>
+        <v>2.2000516122</v>
       </c>
       <c r="Q2">
-        <v>3.3013</v>
+        <v>3.2900516122</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08148062653468752</v>
+        <v>0.08176174662253657</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8305253261555789</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.5881723956921</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08133646915631121</v>
+        <v>0.08119231177793489</v>
       </c>
       <c r="C3">
-        <v>27.15897725450182</v>
+        <v>26.9773870535897</v>
       </c>
       <c r="D3">
-        <v>25.80567725450182</v>
+        <v>25.9107870535897</v>
       </c>
       <c r="E3">
-        <v>-5.5833</v>
+        <v>-5.2966</v>
       </c>
       <c r="F3">
-        <v>0.2867</v>
+        <v>0.5734</v>
       </c>
       <c r="G3">
         <v>1.64</v>
@@ -1515,28 +1515,28 @@
         <v>2.835</v>
       </c>
       <c r="M3">
-        <v>0.01442101</v>
+        <v>0.02884202</v>
       </c>
       <c r="N3">
-        <v>2.82057899</v>
+        <v>2.80615798</v>
       </c>
       <c r="O3">
-        <v>0.6205273778</v>
+        <v>0.6173547556</v>
       </c>
       <c r="P3">
-        <v>2.2000516122</v>
+        <v>2.1888032244</v>
       </c>
       <c r="Q3">
-        <v>3.2900516122</v>
+        <v>3.2788032244</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08176174662253657</v>
+        <v>0.08204860385503561</v>
       </c>
       <c r="T3">
-        <v>0.8305253261555789</v>
+        <v>0.8371502045042865</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.5881723956921</v>
+        <v>98.29408619784606</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08119231177793489</v>
+        <v>0.08104815439955858</v>
       </c>
       <c r="C4">
-        <v>26.9773870535897</v>
+        <v>26.79665660566813</v>
       </c>
       <c r="D4">
-        <v>25.9107870535897</v>
+        <v>26.01675660566812</v>
       </c>
       <c r="E4">
-        <v>-5.2966</v>
+        <v>-5.0099</v>
       </c>
       <c r="F4">
-        <v>0.5734</v>
+        <v>0.8601</v>
       </c>
       <c r="G4">
         <v>1.64</v>
@@ -1597,28 +1597,28 @@
         <v>2.835</v>
       </c>
       <c r="M4">
-        <v>0.02884202</v>
+        <v>0.04326302999999999</v>
       </c>
       <c r="N4">
-        <v>2.80615798</v>
+        <v>2.79173697</v>
       </c>
       <c r="O4">
-        <v>0.6173547556</v>
+        <v>0.6141821334000001</v>
       </c>
       <c r="P4">
-        <v>2.1888032244</v>
+        <v>2.1775548366</v>
       </c>
       <c r="Q4">
-        <v>3.2788032244</v>
+        <v>3.2675548366</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08204860385503561</v>
+        <v>0.08234137566964803</v>
       </c>
       <c r="T4">
-        <v>0.8371502045042865</v>
+        <v>0.8439116782828642</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.29408619784606</v>
+        <v>65.52939079856405</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08104815439955858</v>
+        <v>0.08090399702118227</v>
       </c>
       <c r="C5">
-        <v>26.79665660566813</v>
+        <v>26.61679650267087</v>
       </c>
       <c r="D5">
-        <v>26.01675660566812</v>
+        <v>26.12359650267086</v>
       </c>
       <c r="E5">
-        <v>-5.0099</v>
+        <v>-4.7232</v>
       </c>
       <c r="F5">
-        <v>0.8601</v>
+        <v>1.1468</v>
       </c>
       <c r="G5">
         <v>1.64</v>
@@ -1679,28 +1679,28 @@
         <v>2.835</v>
       </c>
       <c r="M5">
-        <v>0.04326302999999999</v>
+        <v>0.05768404</v>
       </c>
       <c r="N5">
-        <v>2.79173697</v>
+        <v>2.77731596</v>
       </c>
       <c r="O5">
-        <v>0.6141821334000001</v>
+        <v>0.6110095112</v>
       </c>
       <c r="P5">
-        <v>2.1775548366</v>
+        <v>2.1663064488</v>
       </c>
       <c r="Q5">
-        <v>3.2675548366</v>
+        <v>3.2563064488</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08234137566964803</v>
+        <v>0.08264024689706487</v>
       </c>
       <c r="T5">
-        <v>0.8439116782828642</v>
+        <v>0.8508140160984956</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.52939079856405</v>
+        <v>49.14704309892304</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08090399702118227</v>
+        <v>0.08075983964280595</v>
       </c>
       <c r="C6">
-        <v>26.61679650267087</v>
+        <v>26.43781751123564</v>
       </c>
       <c r="D6">
-        <v>26.12359650267086</v>
+        <v>26.23131751123564</v>
       </c>
       <c r="E6">
-        <v>-4.7232</v>
+        <v>-4.4365</v>
       </c>
       <c r="F6">
-        <v>1.1468</v>
+        <v>1.4335</v>
       </c>
       <c r="G6">
         <v>1.64</v>
@@ -1761,28 +1761,28 @@
         <v>2.835</v>
       </c>
       <c r="M6">
-        <v>0.05768404</v>
+        <v>0.07210505</v>
       </c>
       <c r="N6">
-        <v>2.77731596</v>
+        <v>2.76289495</v>
       </c>
       <c r="O6">
-        <v>0.6110095112</v>
+        <v>0.607836889</v>
       </c>
       <c r="P6">
-        <v>2.1663064488</v>
+        <v>2.155058061</v>
       </c>
       <c r="Q6">
-        <v>3.2563064488</v>
+        <v>3.245058061</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08264024689706487</v>
+        <v>0.08294541015032206</v>
       </c>
       <c r="T6">
-        <v>0.8508140160984956</v>
+        <v>0.857861666289193</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.14704309892304</v>
+        <v>39.31763447913842</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08075983964280595</v>
+        <v>0.08061568226442965</v>
       </c>
       <c r="C7">
-        <v>26.43781751123564</v>
+        <v>26.25973057632095</v>
       </c>
       <c r="D7">
-        <v>26.23131751123564</v>
+        <v>26.33993057632095</v>
       </c>
       <c r="E7">
-        <v>-4.4365</v>
+        <v>-4.1498</v>
       </c>
       <c r="F7">
-        <v>1.4335</v>
+        <v>1.7202</v>
       </c>
       <c r="G7">
         <v>1.64</v>
@@ -1843,28 +1843,28 @@
         <v>2.835</v>
       </c>
       <c r="M7">
-        <v>0.07210505</v>
+        <v>0.08652606</v>
       </c>
       <c r="N7">
-        <v>2.76289495</v>
+        <v>2.74847394</v>
       </c>
       <c r="O7">
-        <v>0.607836889</v>
+        <v>0.6046642668</v>
       </c>
       <c r="P7">
-        <v>2.155058061</v>
+        <v>2.1438096732</v>
       </c>
       <c r="Q7">
-        <v>3.245058061</v>
+        <v>3.2338096732</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08294541015032206</v>
+        <v>0.08325706623875495</v>
       </c>
       <c r="T7">
-        <v>0.857861666289193</v>
+        <v>0.8650592664839477</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.31763447913842</v>
+        <v>32.76469539928202</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08061568226442965</v>
+        <v>0.08047152488605333</v>
       </c>
       <c r="C8">
-        <v>26.25973057632095</v>
+        <v>26.08254682491329</v>
       </c>
       <c r="D8">
-        <v>26.33993057632095</v>
+        <v>26.4494468249133</v>
       </c>
       <c r="E8">
-        <v>-4.1498</v>
+        <v>-3.8631</v>
       </c>
       <c r="F8">
-        <v>1.7202</v>
+        <v>2.0069</v>
       </c>
       <c r="G8">
         <v>1.64</v>
@@ -1925,28 +1925,28 @@
         <v>2.835</v>
       </c>
       <c r="M8">
-        <v>0.08652605999999999</v>
+        <v>0.10094707</v>
       </c>
       <c r="N8">
-        <v>2.74847394</v>
+        <v>2.73405293</v>
       </c>
       <c r="O8">
-        <v>0.6046642668</v>
+        <v>0.6014916445999999</v>
       </c>
       <c r="P8">
-        <v>2.1438096732</v>
+        <v>2.1325612854</v>
       </c>
       <c r="Q8">
-        <v>3.2338096732</v>
+        <v>3.2225612854</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08325706623875495</v>
+        <v>0.08357542460865949</v>
       </c>
       <c r="T8">
-        <v>0.8650592664839477</v>
+        <v>0.8724116537796649</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.76469539928202</v>
+        <v>28.08402462795602</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08047152488605333</v>
+        <v>0.08032736750767701</v>
       </c>
       <c r="C9">
-        <v>26.08254682491329</v>
+        <v>25.90627756982704</v>
       </c>
       <c r="D9">
-        <v>26.4494468249133</v>
+        <v>26.55987756982704</v>
       </c>
       <c r="E9">
-        <v>-3.8631</v>
+        <v>-3.5764</v>
       </c>
       <c r="F9">
-        <v>2.0069</v>
+        <v>2.2936</v>
       </c>
       <c r="G9">
         <v>1.64</v>
@@ -2007,28 +2007,28 @@
         <v>2.835</v>
       </c>
       <c r="M9">
-        <v>0.10094707</v>
+        <v>0.11536808</v>
       </c>
       <c r="N9">
-        <v>2.73405293</v>
+        <v>2.71963192</v>
       </c>
       <c r="O9">
-        <v>0.6014916445999999</v>
+        <v>0.5983190224</v>
       </c>
       <c r="P9">
-        <v>2.1325612854</v>
+        <v>2.1213128976</v>
       </c>
       <c r="Q9">
-        <v>3.2225612854</v>
+        <v>3.2113128976</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08357542460865949</v>
+        <v>0.08390070381269241</v>
       </c>
       <c r="T9">
-        <v>0.872411653779665</v>
+        <v>0.8799238755818108</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.08402462795601</v>
+        <v>24.57352154946151</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08032736750767701</v>
+        <v>0.08018321012930071</v>
       </c>
       <c r="C10">
-        <v>25.90627756982704</v>
+        <v>25.73093431360004</v>
       </c>
       <c r="D10">
-        <v>26.55987756982704</v>
+        <v>26.67123431360004</v>
       </c>
       <c r="E10">
-        <v>-3.5764</v>
+        <v>-3.2897</v>
       </c>
       <c r="F10">
-        <v>2.2936</v>
+        <v>2.5803</v>
       </c>
       <c r="G10">
         <v>1.64</v>
@@ -2089,28 +2089,28 @@
         <v>2.835</v>
       </c>
       <c r="M10">
-        <v>0.11536808</v>
+        <v>0.12978909</v>
       </c>
       <c r="N10">
-        <v>2.71963192</v>
+        <v>2.70521091</v>
       </c>
       <c r="O10">
-        <v>0.5983190224</v>
+        <v>0.5951464002</v>
       </c>
       <c r="P10">
-        <v>2.1213128976</v>
+        <v>2.1100645098</v>
       </c>
       <c r="Q10">
-        <v>3.2113128976</v>
+        <v>3.2000645098</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08390070381269241</v>
+        <v>0.08423313201022056</v>
       </c>
       <c r="T10">
-        <v>0.8799238755818108</v>
+        <v>0.887601201159828</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.57352154946151</v>
+        <v>21.84313026618801</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08018321012930071</v>
+        <v>0.08003905275092439</v>
       </c>
       <c r="C11">
-        <v>25.73093431360004</v>
+        <v>25.55652875248767</v>
       </c>
       <c r="D11">
-        <v>26.67123431360004</v>
+        <v>26.78352875248767</v>
       </c>
       <c r="E11">
-        <v>-3.2897</v>
+        <v>-3.003</v>
       </c>
       <c r="F11">
-        <v>2.5803</v>
+        <v>2.867</v>
       </c>
       <c r="G11">
         <v>1.64</v>
@@ -2171,28 +2171,28 @@
         <v>2.835</v>
       </c>
       <c r="M11">
-        <v>0.12978909</v>
+        <v>0.1442101</v>
       </c>
       <c r="N11">
-        <v>2.70521091</v>
+        <v>2.6907899</v>
       </c>
       <c r="O11">
-        <v>0.5951464002</v>
+        <v>0.591973778</v>
       </c>
       <c r="P11">
-        <v>2.1100645098</v>
+        <v>2.098816122</v>
       </c>
       <c r="Q11">
-        <v>3.2000645098</v>
+        <v>3.188816122</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08423313201022056</v>
+        <v>0.0845729475010271</v>
       </c>
       <c r="T11">
-        <v>0.887601201159828</v>
+        <v>0.8954491339729123</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.84313026618801</v>
+        <v>19.65881723956921</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08003905275092439</v>
+        <v>0.07989489537254808</v>
       </c>
       <c r="C12">
-        <v>25.55652875248767</v>
+        <v>25.38307278055804</v>
       </c>
       <c r="D12">
-        <v>26.78352875248767</v>
+        <v>26.89677278055804</v>
       </c>
       <c r="E12">
-        <v>-3.003</v>
+        <v>-2.7163</v>
       </c>
       <c r="F12">
-        <v>2.867</v>
+        <v>3.1537</v>
       </c>
       <c r="G12">
         <v>1.64</v>
@@ -2253,28 +2253,28 @@
         <v>2.835</v>
       </c>
       <c r="M12">
-        <v>0.1442101</v>
+        <v>0.15863111</v>
       </c>
       <c r="N12">
-        <v>2.6907899</v>
+        <v>2.67636889</v>
       </c>
       <c r="O12">
-        <v>0.591973778</v>
+        <v>0.5888011558</v>
       </c>
       <c r="P12">
-        <v>2.098816122</v>
+        <v>2.0875677342</v>
       </c>
       <c r="Q12">
-        <v>3.188816122</v>
+        <v>3.1775677342</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0845729475010271</v>
+        <v>0.08492039929499785</v>
       </c>
       <c r="T12">
-        <v>0.8954491339729123</v>
+        <v>0.9034734248267401</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.65881723956921</v>
+        <v>17.87165203597201</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07989489537254808</v>
+        <v>0.07975073799417177</v>
       </c>
       <c r="C13">
-        <v>25.38307278055804</v>
+        <v>25.2105784938917</v>
       </c>
       <c r="D13">
-        <v>26.89677278055804</v>
+        <v>27.0109784938917</v>
       </c>
       <c r="E13">
-        <v>-2.7163</v>
+        <v>-2.4296</v>
       </c>
       <c r="F13">
-        <v>3.1537</v>
+        <v>3.4404</v>
       </c>
       <c r="G13">
         <v>1.64</v>
@@ -2335,28 +2335,28 @@
         <v>2.835</v>
       </c>
       <c r="M13">
-        <v>0.15863111</v>
+        <v>0.17305212</v>
       </c>
       <c r="N13">
-        <v>2.67636889</v>
+        <v>2.66194788</v>
       </c>
       <c r="O13">
-        <v>0.5888011558</v>
+        <v>0.5856285336</v>
       </c>
       <c r="P13">
-        <v>2.0875677342</v>
+        <v>2.0763193464</v>
       </c>
       <c r="Q13">
-        <v>3.1775677342</v>
+        <v>3.1663193464</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08492039929499785</v>
+        <v>0.08527574772064975</v>
       </c>
       <c r="T13">
-        <v>0.9034734248267401</v>
+        <v>0.9116800859272457</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.87165203597201</v>
+        <v>16.38234769964101</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07975073799417177</v>
+        <v>0.07960658061579545</v>
       </c>
       <c r="C14">
-        <v>25.2105784938917</v>
+        <v>25.03905819488871</v>
       </c>
       <c r="D14">
-        <v>27.0109784938917</v>
+        <v>27.12615819488871</v>
       </c>
       <c r="E14">
-        <v>-2.4296</v>
+        <v>-2.1429</v>
       </c>
       <c r="F14">
-        <v>3.4404</v>
+        <v>3.727100000000001</v>
       </c>
       <c r="G14">
         <v>1.64</v>
@@ -2417,28 +2417,28 @@
         <v>2.835</v>
       </c>
       <c r="M14">
-        <v>0.17305212</v>
+        <v>0.18747313</v>
       </c>
       <c r="N14">
-        <v>2.66194788</v>
+        <v>2.64752687</v>
       </c>
       <c r="O14">
-        <v>0.5856285336</v>
+        <v>0.5824559114</v>
       </c>
       <c r="P14">
-        <v>2.0763193464</v>
+        <v>2.0650709586</v>
       </c>
       <c r="Q14">
-        <v>3.1663193464</v>
+        <v>3.155070958600001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08527574772064975</v>
+        <v>0.08563926507562697</v>
       </c>
       <c r="T14">
-        <v>0.9116800859272457</v>
+        <v>0.9200754059036249</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.38234769964101</v>
+        <v>15.12216710736093</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07960658061579545</v>
+        <v>0.07946242323741914</v>
       </c>
       <c r="C15">
-        <v>25.03905819488871</v>
+        <v>24.86852439668637</v>
       </c>
       <c r="D15">
-        <v>27.12615819488871</v>
+        <v>27.24232439668637</v>
       </c>
       <c r="E15">
-        <v>-2.1429</v>
+        <v>-1.856199999999999</v>
       </c>
       <c r="F15">
-        <v>3.727100000000001</v>
+        <v>4.013800000000001</v>
       </c>
       <c r="G15">
         <v>1.64</v>
@@ -2499,28 +2499,28 @@
         <v>2.835</v>
       </c>
       <c r="M15">
-        <v>0.18747313</v>
+        <v>0.20189414</v>
       </c>
       <c r="N15">
-        <v>2.64752687</v>
+        <v>2.63310586</v>
       </c>
       <c r="O15">
-        <v>0.5824559114</v>
+        <v>0.5792832892000001</v>
       </c>
       <c r="P15">
-        <v>2.0650709586</v>
+        <v>2.0538225708</v>
       </c>
       <c r="Q15">
-        <v>3.155070958600001</v>
+        <v>3.1438225708</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08563926507562697</v>
+        <v>0.0860112363225804</v>
       </c>
       <c r="T15">
-        <v>0.9200754059036249</v>
+        <v>0.9286659658794549</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.12216710736093</v>
+        <v>14.04201231397801</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07946242323741914</v>
+        <v>0.07931826585904282</v>
       </c>
       <c r="C16">
-        <v>24.86852439668637</v>
+        <v>24.69898982769103</v>
       </c>
       <c r="D16">
-        <v>27.24232439668637</v>
+        <v>27.35948982769103</v>
       </c>
       <c r="E16">
-        <v>-1.856199999999999</v>
+        <v>-1.569499999999999</v>
       </c>
       <c r="F16">
-        <v>4.013800000000001</v>
+        <v>4.300500000000001</v>
       </c>
       <c r="G16">
         <v>1.64</v>
@@ -2581,28 +2581,28 @@
         <v>2.835</v>
       </c>
       <c r="M16">
-        <v>0.20189414</v>
+        <v>0.2163151500000001</v>
       </c>
       <c r="N16">
-        <v>2.63310586</v>
+        <v>2.61868485</v>
       </c>
       <c r="O16">
-        <v>0.5792832892000001</v>
+        <v>0.5761106669999999</v>
       </c>
       <c r="P16">
-        <v>2.0538225708</v>
+        <v>2.042574183</v>
       </c>
       <c r="Q16">
-        <v>3.1438225708</v>
+        <v>3.132574183</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0860112363225804</v>
+        <v>0.08639195983416803</v>
       </c>
       <c r="T16">
-        <v>0.9286659658794549</v>
+        <v>0.9374586566782456</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.04201231397801</v>
+        <v>13.1058781597128</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07931826585904282</v>
+        <v>0.0793613084806665</v>
       </c>
       <c r="C17">
-        <v>24.69898982769103</v>
+        <v>24.37720108348582</v>
       </c>
       <c r="D17">
-        <v>27.35948982769103</v>
+        <v>27.32440108348582</v>
       </c>
       <c r="E17">
-        <v>-1.5695</v>
+        <v>-1.2828</v>
       </c>
       <c r="F17">
-        <v>4.3005</v>
+        <v>4.5872</v>
       </c>
       <c r="G17">
         <v>1.64</v>
@@ -2663,45 +2663,45 @@
         <v>2.835</v>
       </c>
       <c r="M17">
-        <v>0.21631515</v>
+        <v>0.23761696</v>
       </c>
       <c r="N17">
-        <v>2.61868485</v>
+        <v>2.59738304</v>
       </c>
       <c r="O17">
-        <v>0.576110667</v>
+        <v>0.5714242688</v>
       </c>
       <c r="P17">
-        <v>2.042574183</v>
+        <v>2.0259587712</v>
       </c>
       <c r="Q17">
-        <v>3.132574183</v>
+        <v>3.1159587712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08639195983416803</v>
+        <v>0.08678174819126966</v>
       </c>
       <c r="T17">
-        <v>0.9374586566782456</v>
+        <v>0.9464606972579599</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.10587815971281</v>
+        <v>11.93096654380226</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0793613084806665</v>
+        <v>0.07922885110229021</v>
       </c>
       <c r="C18">
-        <v>24.37720108348582</v>
+        <v>24.19877039020373</v>
       </c>
       <c r="D18">
-        <v>27.32440108348582</v>
+        <v>27.43267039020373</v>
       </c>
       <c r="E18">
-        <v>-1.2828</v>
+        <v>-0.9960999999999993</v>
       </c>
       <c r="F18">
-        <v>4.5872</v>
+        <v>4.873900000000001</v>
       </c>
       <c r="G18">
         <v>1.64</v>
@@ -2745,28 +2745,28 @@
         <v>2.835</v>
       </c>
       <c r="M18">
-        <v>0.23761696</v>
+        <v>0.25246802</v>
       </c>
       <c r="N18">
-        <v>2.59738304</v>
+        <v>2.58253198</v>
       </c>
       <c r="O18">
-        <v>0.5714242688</v>
+        <v>0.5681570356</v>
       </c>
       <c r="P18">
-        <v>2.0259587712</v>
+        <v>2.0143749444</v>
       </c>
       <c r="Q18">
-        <v>3.1159587712</v>
+        <v>3.1043749444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08678174819126966</v>
+        <v>0.08718092903890387</v>
       </c>
       <c r="T18">
-        <v>0.9464606972579599</v>
+        <v>0.9556796544781493</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.93096654380226</v>
+        <v>11.22914498240213</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07922885110229021</v>
+        <v>0.07909639372391389</v>
       </c>
       <c r="C19">
-        <v>24.19877039020373</v>
+        <v>24.02120111564737</v>
       </c>
       <c r="D19">
-        <v>27.43267039020373</v>
+        <v>27.54180111564737</v>
       </c>
       <c r="E19">
-        <v>-0.9960999999999993</v>
+        <v>-0.7093999999999996</v>
       </c>
       <c r="F19">
-        <v>4.873900000000001</v>
+        <v>5.160600000000001</v>
       </c>
       <c r="G19">
         <v>1.64</v>
@@ -2827,28 +2827,28 @@
         <v>2.835</v>
       </c>
       <c r="M19">
-        <v>0.25246802</v>
+        <v>0.26731908</v>
       </c>
       <c r="N19">
-        <v>2.58253198</v>
+        <v>2.56768092</v>
       </c>
       <c r="O19">
-        <v>0.5681570356</v>
+        <v>0.5648898024</v>
       </c>
       <c r="P19">
-        <v>2.0143749444</v>
+        <v>2.0027911176</v>
       </c>
       <c r="Q19">
-        <v>3.1043749444</v>
+        <v>3.0927911176</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08718092903890387</v>
+        <v>0.08758984600477304</v>
       </c>
       <c r="T19">
-        <v>0.9556796544781493</v>
+        <v>0.9651234643134652</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.22914498240213</v>
+        <v>10.6053035944909</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0790963937239139</v>
+        <v>0.0789639363455376</v>
       </c>
       <c r="C20">
-        <v>24.02120111564736</v>
+        <v>23.84450358138395</v>
       </c>
       <c r="D20">
-        <v>27.54180111564736</v>
+        <v>27.65180358138394</v>
       </c>
       <c r="E20">
-        <v>-0.7093999999999996</v>
+        <v>-0.4226999999999999</v>
       </c>
       <c r="F20">
-        <v>5.160600000000001</v>
+        <v>5.4473</v>
       </c>
       <c r="G20">
         <v>1.64</v>
@@ -2909,28 +2909,28 @@
         <v>2.835</v>
       </c>
       <c r="M20">
-        <v>0.26731908</v>
+        <v>0.28217014</v>
       </c>
       <c r="N20">
-        <v>2.56768092</v>
+        <v>2.55282986</v>
       </c>
       <c r="O20">
-        <v>0.5648898024</v>
+        <v>0.5616225692</v>
       </c>
       <c r="P20">
-        <v>2.0027911176</v>
+        <v>1.9912072908</v>
       </c>
       <c r="Q20">
-        <v>3.0927911176</v>
+        <v>3.0812072908</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08758984600477304</v>
+        <v>0.08800885968584887</v>
       </c>
       <c r="T20">
-        <v>0.965123464313465</v>
+        <v>0.9748004546385418</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.6053035944909</v>
+        <v>10.04712972109664</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0789639363455376</v>
+        <v>0.07909667896716129</v>
       </c>
       <c r="C21">
-        <v>23.84450358138395</v>
+        <v>23.44756517281364</v>
       </c>
       <c r="D21">
-        <v>27.65180358138394</v>
+        <v>27.54156517281364</v>
       </c>
       <c r="E21">
-        <v>-0.4226999999999999</v>
+        <v>-0.1359999999999992</v>
       </c>
       <c r="F21">
-        <v>5.4473</v>
+        <v>5.734000000000001</v>
       </c>
       <c r="G21">
         <v>1.64</v>
@@ -2991,45 +2991,45 @@
         <v>2.835</v>
       </c>
       <c r="M21">
-        <v>0.28217014</v>
+        <v>0.306769</v>
       </c>
       <c r="N21">
-        <v>2.55282986</v>
+        <v>2.528231</v>
       </c>
       <c r="O21">
-        <v>0.5616225692</v>
+        <v>0.55621082</v>
       </c>
       <c r="P21">
-        <v>1.9912072908</v>
+        <v>1.97202018</v>
       </c>
       <c r="Q21">
-        <v>3.0812072908</v>
+        <v>3.06202018</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08800885968584887</v>
+        <v>0.08843834870895159</v>
       </c>
       <c r="T21">
-        <v>0.9748004546385418</v>
+        <v>0.9847193697217456</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.04712972109664</v>
+        <v>9.241481375236742</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07909667896716129</v>
+        <v>0.07897748158878497</v>
       </c>
       <c r="C22">
-        <v>23.44756517281364</v>
+        <v>23.25981428551813</v>
       </c>
       <c r="D22">
-        <v>27.54156517281364</v>
+        <v>27.64051428551813</v>
       </c>
       <c r="E22">
-        <v>-0.1359999999999992</v>
+        <v>0.1507000000000005</v>
       </c>
       <c r="F22">
-        <v>5.734000000000001</v>
+        <v>6.020700000000001</v>
       </c>
       <c r="G22">
         <v>1.64</v>
@@ -3073,28 +3073,28 @@
         <v>2.835</v>
       </c>
       <c r="M22">
-        <v>0.306769</v>
+        <v>0.32210745</v>
       </c>
       <c r="N22">
-        <v>2.528231</v>
+        <v>2.51289255</v>
       </c>
       <c r="O22">
-        <v>0.55621082</v>
+        <v>0.552836361</v>
       </c>
       <c r="P22">
-        <v>1.97202018</v>
+        <v>1.960056189</v>
       </c>
       <c r="Q22">
-        <v>3.06202018</v>
+        <v>3.050056189</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08843834870895159</v>
+        <v>0.08887871087187969</v>
       </c>
       <c r="T22">
-        <v>0.9847193697217456</v>
+        <v>0.9948893965792076</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.241481375236742</v>
+        <v>8.801410833558801</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07897748158878497</v>
+        <v>0.07885828421040864</v>
       </c>
       <c r="C23">
-        <v>23.25981428551813</v>
+        <v>23.07277695460396</v>
       </c>
       <c r="D23">
-        <v>27.64051428551813</v>
+        <v>27.74017695460396</v>
       </c>
       <c r="E23">
-        <v>0.1506999999999996</v>
+        <v>0.4374000000000002</v>
       </c>
       <c r="F23">
-        <v>6.0207</v>
+        <v>6.3074</v>
       </c>
       <c r="G23">
         <v>1.64</v>
@@ -3155,28 +3155,28 @@
         <v>2.835</v>
       </c>
       <c r="M23">
-        <v>0.32210745</v>
+        <v>0.3374459</v>
       </c>
       <c r="N23">
-        <v>2.51289255</v>
+        <v>2.4975541</v>
       </c>
       <c r="O23">
-        <v>0.552836361</v>
+        <v>0.549461902</v>
       </c>
       <c r="P23">
-        <v>1.960056189</v>
+        <v>1.948092198</v>
       </c>
       <c r="Q23">
-        <v>3.050056189</v>
+        <v>3.038092198</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08887871087187969</v>
+        <v>0.08933036437231877</v>
       </c>
       <c r="T23">
-        <v>0.9948893965792075</v>
+        <v>1.005320193356092</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.801410833558803</v>
+        <v>8.401346704760673</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07885828421040864</v>
+        <v>0.07873908683203235</v>
       </c>
       <c r="C24">
-        <v>23.07277695460396</v>
+        <v>22.88646092655632</v>
       </c>
       <c r="D24">
-        <v>27.74017695460396</v>
+        <v>27.84056092655632</v>
       </c>
       <c r="E24">
-        <v>0.4374000000000002</v>
+        <v>0.7241000000000009</v>
       </c>
       <c r="F24">
-        <v>6.3074</v>
+        <v>6.594100000000001</v>
       </c>
       <c r="G24">
         <v>1.64</v>
@@ -3237,28 +3237,28 @@
         <v>2.835</v>
       </c>
       <c r="M24">
-        <v>0.3374459</v>
+        <v>0.35278435</v>
       </c>
       <c r="N24">
-        <v>2.4975541</v>
+        <v>2.48221565</v>
       </c>
       <c r="O24">
-        <v>0.549461902</v>
+        <v>0.546087443</v>
       </c>
       <c r="P24">
-        <v>1.948092198</v>
+        <v>1.936128207</v>
       </c>
       <c r="Q24">
-        <v>3.038092198</v>
+        <v>3.026128207</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08933036437231877</v>
+        <v>0.08979374913250954</v>
       </c>
       <c r="T24">
-        <v>1.005320193356092</v>
+        <v>1.016021919919389</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.401346704760673</v>
+        <v>8.036070761075427</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07873908683203235</v>
+        <v>0.07861988945365601</v>
       </c>
       <c r="C25">
-        <v>22.88646092655632</v>
+        <v>22.70087406039726</v>
       </c>
       <c r="D25">
-        <v>27.84056092655632</v>
+        <v>27.94167406039726</v>
       </c>
       <c r="E25">
-        <v>0.7241000000000009</v>
+        <v>1.010800000000001</v>
       </c>
       <c r="F25">
-        <v>6.594100000000001</v>
+        <v>6.880800000000001</v>
       </c>
       <c r="G25">
         <v>1.64</v>
@@ -3319,28 +3319,28 @@
         <v>2.835</v>
       </c>
       <c r="M25">
-        <v>0.35278435</v>
+        <v>0.3681228</v>
       </c>
       <c r="N25">
-        <v>2.48221565</v>
+        <v>2.4668772</v>
       </c>
       <c r="O25">
-        <v>0.546087443</v>
+        <v>0.542712984</v>
       </c>
       <c r="P25">
-        <v>1.936128207</v>
+        <v>1.924164216</v>
       </c>
       <c r="Q25">
-        <v>3.026128207</v>
+        <v>3.014164216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08979374913250954</v>
+        <v>0.09026932822849476</v>
       </c>
       <c r="T25">
-        <v>1.016021919919389</v>
+        <v>1.02700527086593</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.036070761075427</v>
+        <v>7.701234479363951</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07861988945365601</v>
+        <v>0.07865669207527971</v>
       </c>
       <c r="C26">
-        <v>22.70087406039726</v>
+        <v>22.38287672664188</v>
       </c>
       <c r="D26">
-        <v>27.94167406039726</v>
+        <v>27.91037672664188</v>
       </c>
       <c r="E26">
-        <v>1.0108</v>
+        <v>1.2975</v>
       </c>
       <c r="F26">
-        <v>6.8808</v>
+        <v>7.1675</v>
       </c>
       <c r="G26">
         <v>1.64</v>
@@ -3401,45 +3401,45 @@
         <v>2.835</v>
       </c>
       <c r="M26">
-        <v>0.3681228</v>
+        <v>0.38919525</v>
       </c>
       <c r="N26">
-        <v>2.4668772</v>
+        <v>2.44580475</v>
       </c>
       <c r="O26">
-        <v>0.542712984</v>
+        <v>0.538077045</v>
       </c>
       <c r="P26">
-        <v>1.924164216</v>
+        <v>1.907727705</v>
       </c>
       <c r="Q26">
-        <v>3.014164216</v>
+        <v>2.997727705</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09026932822849476</v>
+        <v>0.09075758943370628</v>
       </c>
       <c r="T26">
-        <v>1.02700527086593</v>
+        <v>1.038281511171046</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.701234479363952</v>
+        <v>7.284261562801703</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07865669207527971</v>
+        <v>0.0785437346969034</v>
       </c>
       <c r="C27">
-        <v>22.38287672664188</v>
+        <v>22.19246027565423</v>
       </c>
       <c r="D27">
-        <v>27.91037672664188</v>
+        <v>28.00666027565423</v>
       </c>
       <c r="E27">
-        <v>1.2975</v>
+        <v>1.584200000000001</v>
       </c>
       <c r="F27">
-        <v>7.1675</v>
+        <v>7.454200000000001</v>
       </c>
       <c r="G27">
         <v>1.64</v>
@@ -3483,28 +3483,28 @@
         <v>2.835</v>
       </c>
       <c r="M27">
-        <v>0.38919525</v>
+        <v>0.4047630600000001</v>
       </c>
       <c r="N27">
-        <v>2.44580475</v>
+        <v>2.43023694</v>
       </c>
       <c r="O27">
-        <v>0.538077045</v>
+        <v>0.5346521268</v>
       </c>
       <c r="P27">
-        <v>1.907727705</v>
+        <v>1.8955848132</v>
       </c>
       <c r="Q27">
-        <v>2.997727705</v>
+        <v>2.9855848132</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09075758943370628</v>
+        <v>0.09125904688770729</v>
       </c>
       <c r="T27">
-        <v>1.038281511171046</v>
+        <v>1.049862514727651</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.284261562801703</v>
+        <v>7.004097656540099</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0785437346969034</v>
+        <v>0.07843077731852709</v>
       </c>
       <c r="C28">
-        <v>22.19246027565423</v>
+        <v>22.00271043074654</v>
       </c>
       <c r="D28">
-        <v>28.00666027565423</v>
+        <v>28.10361043074654</v>
       </c>
       <c r="E28">
-        <v>1.584200000000001</v>
+        <v>1.870900000000001</v>
       </c>
       <c r="F28">
-        <v>7.454200000000001</v>
+        <v>7.740900000000001</v>
       </c>
       <c r="G28">
         <v>1.64</v>
@@ -3565,28 +3565,28 @@
         <v>2.835</v>
       </c>
       <c r="M28">
-        <v>0.4047630600000001</v>
+        <v>0.42033087</v>
       </c>
       <c r="N28">
-        <v>2.43023694</v>
+        <v>2.41466913</v>
       </c>
       <c r="O28">
-        <v>0.5346521268</v>
+        <v>0.5312272086000001</v>
       </c>
       <c r="P28">
-        <v>1.8955848132</v>
+        <v>1.8834419214</v>
       </c>
       <c r="Q28">
-        <v>2.9855848132</v>
+        <v>2.9734419214</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09125904688770729</v>
+        <v>0.09177424290209189</v>
       </c>
       <c r="T28">
-        <v>1.049862514727651</v>
+        <v>1.06176080605293</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.004097656540099</v>
+        <v>6.7446866322238</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07843077731852709</v>
+        <v>0.07831781994015076</v>
       </c>
       <c r="C29">
-        <v>22.00271043074654</v>
+        <v>21.81363413870142</v>
       </c>
       <c r="D29">
-        <v>28.10361043074654</v>
+        <v>28.20123413870143</v>
       </c>
       <c r="E29">
-        <v>1.870900000000001</v>
+        <v>2.157600000000001</v>
       </c>
       <c r="F29">
-        <v>7.740900000000001</v>
+        <v>8.027600000000001</v>
       </c>
       <c r="G29">
         <v>1.64</v>
@@ -3647,28 +3647,28 @@
         <v>2.835</v>
       </c>
       <c r="M29">
-        <v>0.42033087</v>
+        <v>0.4358986800000001</v>
       </c>
       <c r="N29">
-        <v>2.41466913</v>
+        <v>2.39910132</v>
       </c>
       <c r="O29">
-        <v>0.5312272086000001</v>
+        <v>0.5278022903999999</v>
       </c>
       <c r="P29">
-        <v>1.8834419214</v>
+        <v>1.8712990296</v>
       </c>
       <c r="Q29">
-        <v>2.9734419214</v>
+        <v>2.9612990296</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09177424290209189</v>
+        <v>0.09230374991687607</v>
       </c>
       <c r="T29">
-        <v>1.06176080605293</v>
+        <v>1.073989605470579</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.7446866322238</v>
+        <v>6.503804966787234</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07831781994015076</v>
+        <v>0.07820486256177445</v>
       </c>
       <c r="C30">
-        <v>21.81363413870142</v>
+        <v>21.62523844316227</v>
       </c>
       <c r="D30">
-        <v>28.20123413870143</v>
+        <v>28.29953844316227</v>
       </c>
       <c r="E30">
-        <v>2.157600000000001</v>
+        <v>2.444300000000001</v>
       </c>
       <c r="F30">
-        <v>8.027600000000001</v>
+        <v>8.314300000000001</v>
       </c>
       <c r="G30">
         <v>1.64</v>
@@ -3729,28 +3729,28 @@
         <v>2.835</v>
       </c>
       <c r="M30">
-        <v>0.4358986800000001</v>
+        <v>0.4514664900000001</v>
       </c>
       <c r="N30">
-        <v>2.39910132</v>
+        <v>2.38353351</v>
       </c>
       <c r="O30">
-        <v>0.5278022903999999</v>
+        <v>0.5243773722</v>
       </c>
       <c r="P30">
-        <v>1.8712990296</v>
+        <v>1.8591561378</v>
       </c>
       <c r="Q30">
-        <v>2.9612990296</v>
+        <v>2.9491561378</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09230374991687607</v>
+        <v>0.09284817262221753</v>
       </c>
       <c r="T30">
-        <v>1.073989605470579</v>
+        <v>1.08656287811126</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.503804966787234</v>
+        <v>6.279535830001469</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07820486256177445</v>
+        <v>0.07832590518339815</v>
       </c>
       <c r="C31">
-        <v>21.62523844316227</v>
+        <v>21.23322391603115</v>
       </c>
       <c r="D31">
-        <v>28.29953844316227</v>
+        <v>28.19422391603115</v>
       </c>
       <c r="E31">
-        <v>2.444299999999999</v>
+        <v>2.731000000000001</v>
       </c>
       <c r="F31">
-        <v>8.314299999999999</v>
+        <v>8.601000000000001</v>
       </c>
       <c r="G31">
         <v>1.64</v>
@@ -3811,45 +3811,45 @@
         <v>2.835</v>
       </c>
       <c r="M31">
-        <v>0.45146649</v>
+        <v>0.4756353</v>
       </c>
       <c r="N31">
-        <v>2.38353351</v>
+        <v>2.3593647</v>
       </c>
       <c r="O31">
-        <v>0.5243773722</v>
+        <v>0.519060234</v>
       </c>
       <c r="P31">
-        <v>1.8591561378</v>
+        <v>1.840304466</v>
       </c>
       <c r="Q31">
-        <v>2.9491561378</v>
+        <v>2.930304466</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09284817262221753</v>
+        <v>0.09340815026199735</v>
       </c>
       <c r="T31">
-        <v>1.08656287811126</v>
+        <v>1.099495387113103</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.279535830001469</v>
+        <v>5.960449108802479</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07832590518339815</v>
+        <v>0.07822074780502183</v>
       </c>
       <c r="C32">
-        <v>21.23322391603115</v>
+        <v>21.03797247515123</v>
       </c>
       <c r="D32">
-        <v>28.19422391603115</v>
+        <v>28.28567247515123</v>
       </c>
       <c r="E32">
-        <v>2.731000000000001</v>
+        <v>3.0177</v>
       </c>
       <c r="F32">
-        <v>8.601000000000001</v>
+        <v>8.887700000000001</v>
       </c>
       <c r="G32">
         <v>1.64</v>
@@ -3893,28 +3893,28 @@
         <v>2.835</v>
       </c>
       <c r="M32">
-        <v>0.4756353</v>
+        <v>0.49148981</v>
       </c>
       <c r="N32">
-        <v>2.3593647</v>
+        <v>2.34351019</v>
       </c>
       <c r="O32">
-        <v>0.519060234</v>
+        <v>0.5155722417999999</v>
       </c>
       <c r="P32">
-        <v>1.840304466</v>
+        <v>1.8279379482</v>
       </c>
       <c r="Q32">
-        <v>2.930304466</v>
+        <v>2.9179379482</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09340815026199735</v>
+        <v>0.0939843591377128</v>
       </c>
       <c r="T32">
-        <v>1.099495387113103</v>
+        <v>1.112802751448333</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.960449108802479</v>
+        <v>5.768176556905625</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07822074780502183</v>
+        <v>0.07811559042664552</v>
       </c>
       <c r="C33">
-        <v>21.03797247515123</v>
+        <v>20.84331619534411</v>
       </c>
       <c r="D33">
-        <v>28.28567247515123</v>
+        <v>28.37771619534411</v>
       </c>
       <c r="E33">
-        <v>3.0177</v>
+        <v>3.3044</v>
       </c>
       <c r="F33">
-        <v>8.887700000000001</v>
+        <v>9.1744</v>
       </c>
       <c r="G33">
         <v>1.64</v>
@@ -3975,28 +3975,28 @@
         <v>2.835</v>
       </c>
       <c r="M33">
-        <v>0.49148981</v>
+        <v>0.5073443200000001</v>
       </c>
       <c r="N33">
-        <v>2.34351019</v>
+        <v>2.32765568</v>
       </c>
       <c r="O33">
-        <v>0.5155722417999999</v>
+        <v>0.5120842496</v>
       </c>
       <c r="P33">
-        <v>1.8279379482</v>
+        <v>1.8155714304</v>
       </c>
       <c r="Q33">
-        <v>2.9179379482</v>
+        <v>2.9055714304</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0939843591377128</v>
+        <v>0.09457751533330225</v>
       </c>
       <c r="T33">
-        <v>1.112802751448333</v>
+        <v>1.126501508852246</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.768176556905625</v>
+        <v>5.587921039502324</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07811559042664552</v>
+        <v>0.0780104330482692</v>
       </c>
       <c r="C34">
-        <v>20.84331619534411</v>
+        <v>20.64926090567563</v>
       </c>
       <c r="D34">
-        <v>28.37771619534411</v>
+        <v>28.47036090567563</v>
       </c>
       <c r="E34">
-        <v>3.3044</v>
+        <v>3.591100000000002</v>
       </c>
       <c r="F34">
-        <v>9.1744</v>
+        <v>9.461100000000002</v>
       </c>
       <c r="G34">
         <v>1.64</v>
@@ -4057,28 +4057,28 @@
         <v>2.835</v>
       </c>
       <c r="M34">
-        <v>0.5073443200000001</v>
+        <v>0.5231988300000001</v>
       </c>
       <c r="N34">
-        <v>2.32765568</v>
+        <v>2.31180117</v>
       </c>
       <c r="O34">
-        <v>0.5120842496</v>
+        <v>0.5085962573999999</v>
       </c>
       <c r="P34">
-        <v>1.8155714304</v>
+        <v>1.8032049126</v>
       </c>
       <c r="Q34">
-        <v>2.9055714304</v>
+        <v>2.8932049126</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09457751533330225</v>
+        <v>0.09518837768398389</v>
       </c>
       <c r="T34">
-        <v>1.126501508852246</v>
+        <v>1.140609184387618</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.587921039502324</v>
+        <v>5.418590098911344</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0780104330482692</v>
+        <v>0.0779052756698929</v>
       </c>
       <c r="C35">
-        <v>20.64926090567563</v>
+        <v>20.45581251158149</v>
       </c>
       <c r="D35">
-        <v>28.47036090567563</v>
+        <v>28.56361251158149</v>
       </c>
       <c r="E35">
-        <v>3.591100000000002</v>
+        <v>3.877800000000001</v>
       </c>
       <c r="F35">
-        <v>9.461100000000002</v>
+        <v>9.747800000000002</v>
       </c>
       <c r="G35">
         <v>1.64</v>
@@ -4139,28 +4139,28 @@
         <v>2.835</v>
       </c>
       <c r="M35">
-        <v>0.5231988300000001</v>
+        <v>0.5390533400000002</v>
       </c>
       <c r="N35">
-        <v>2.31180117</v>
+        <v>2.29594666</v>
       </c>
       <c r="O35">
-        <v>0.5085962573999999</v>
+        <v>0.5051082652</v>
       </c>
       <c r="P35">
-        <v>1.8032049126</v>
+        <v>1.7908383948</v>
       </c>
       <c r="Q35">
-        <v>2.8932049126</v>
+        <v>2.8808383948</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09518837768398389</v>
+        <v>0.09581775101498924</v>
       </c>
       <c r="T35">
-        <v>1.140609184387618</v>
+        <v>1.155144365242246</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.418590098911344</v>
+        <v>5.259219801884539</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0779052756698929</v>
+        <v>0.07780011829151656</v>
       </c>
       <c r="C36">
-        <v>20.45581251158149</v>
+        <v>20.26297699612222</v>
       </c>
       <c r="D36">
-        <v>28.56361251158149</v>
+        <v>28.65747699612222</v>
       </c>
       <c r="E36">
-        <v>3.877800000000001</v>
+        <v>4.164500000000001</v>
       </c>
       <c r="F36">
-        <v>9.747800000000002</v>
+        <v>10.0345</v>
       </c>
       <c r="G36">
         <v>1.64</v>
@@ -4221,28 +4221,28 @@
         <v>2.835</v>
       </c>
       <c r="M36">
-        <v>0.5390533400000002</v>
+        <v>0.5549078500000001</v>
       </c>
       <c r="N36">
-        <v>2.29594666</v>
+        <v>2.28009215</v>
       </c>
       <c r="O36">
-        <v>0.5051082652</v>
+        <v>0.501620273</v>
       </c>
       <c r="P36">
-        <v>1.7908383948</v>
+        <v>1.778471877</v>
       </c>
       <c r="Q36">
-        <v>2.8808383948</v>
+        <v>2.868471877</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09581775101498924</v>
+        <v>0.09646648967925628</v>
       </c>
       <c r="T36">
-        <v>1.155144365242246</v>
+        <v>1.170126782430861</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.259219801884539</v>
+        <v>5.108956378973553</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07780011829151656</v>
+        <v>0.07769496091314027</v>
       </c>
       <c r="C37">
-        <v>20.26297699612222</v>
+        <v>20.07076042126257</v>
       </c>
       <c r="D37">
-        <v>28.65747699612222</v>
+        <v>28.75196042126257</v>
       </c>
       <c r="E37">
-        <v>4.164500000000001</v>
+        <v>4.451200000000001</v>
       </c>
       <c r="F37">
-        <v>10.0345</v>
+        <v>10.3212</v>
       </c>
       <c r="G37">
         <v>1.64</v>
@@ -4303,28 +4303,28 @@
         <v>2.835</v>
       </c>
       <c r="M37">
-        <v>0.5549078500000001</v>
+        <v>0.57076236</v>
       </c>
       <c r="N37">
-        <v>2.28009215</v>
+        <v>2.26423764</v>
       </c>
       <c r="O37">
-        <v>0.501620273</v>
+        <v>0.4981322808</v>
       </c>
       <c r="P37">
-        <v>1.778471877</v>
+        <v>1.7661053592</v>
       </c>
       <c r="Q37">
-        <v>2.868471877</v>
+        <v>2.8561053592</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09646648967925628</v>
+        <v>0.09713550142678168</v>
       </c>
       <c r="T37">
-        <v>1.170126782430861</v>
+        <v>1.185577400156621</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.108956378973553</v>
+        <v>4.967040924002067</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07769496091314028</v>
+        <v>0.07758980353476397</v>
       </c>
       <c r="C38">
-        <v>20.07076042126256</v>
+        <v>19.87916892917683</v>
       </c>
       <c r="D38">
-        <v>28.75196042126256</v>
+        <v>28.84706892917684</v>
       </c>
       <c r="E38">
-        <v>4.451200000000001</v>
+        <v>4.737900000000001</v>
       </c>
       <c r="F38">
-        <v>10.3212</v>
+        <v>10.6079</v>
       </c>
       <c r="G38">
         <v>1.64</v>
@@ -4385,28 +4385,28 @@
         <v>2.835</v>
       </c>
       <c r="M38">
-        <v>0.57076236</v>
+        <v>0.5866168700000001</v>
       </c>
       <c r="N38">
-        <v>2.26423764</v>
+        <v>2.24838313</v>
       </c>
       <c r="O38">
-        <v>0.4981322808</v>
+        <v>0.4946442885999999</v>
       </c>
       <c r="P38">
-        <v>1.7661053592</v>
+        <v>1.7537388414</v>
       </c>
       <c r="Q38">
-        <v>2.8561053592</v>
+        <v>2.8437388414</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09713550142678168</v>
+        <v>0.09782575164248247</v>
       </c>
       <c r="T38">
-        <v>1.18557740015662</v>
+        <v>1.201518513683198</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.967040924002067</v>
+        <v>4.832796574704712</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07758980353476397</v>
+        <v>0.07748464615638764</v>
       </c>
       <c r="C39">
-        <v>19.87916892917683</v>
+        <v>19.68820874357971</v>
       </c>
       <c r="D39">
-        <v>28.84706892917684</v>
+        <v>28.94280874357971</v>
       </c>
       <c r="E39">
-        <v>4.737900000000001</v>
+        <v>5.0246</v>
       </c>
       <c r="F39">
-        <v>10.6079</v>
+        <v>10.8946</v>
       </c>
       <c r="G39">
         <v>1.64</v>
@@ -4467,28 +4467,28 @@
         <v>2.835</v>
       </c>
       <c r="M39">
-        <v>0.5866168700000001</v>
+        <v>0.60247138</v>
       </c>
       <c r="N39">
-        <v>2.24838313</v>
+        <v>2.23252862</v>
       </c>
       <c r="O39">
-        <v>0.4946442885999999</v>
+        <v>0.4911562964</v>
       </c>
       <c r="P39">
-        <v>1.7537388414</v>
+        <v>1.7413723236</v>
       </c>
       <c r="Q39">
-        <v>2.8437388414</v>
+        <v>2.8313723236</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09782575164248247</v>
+        <v>0.09853826799417362</v>
       </c>
       <c r="T39">
-        <v>1.201518513683198</v>
+        <v>1.217973856678374</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.832796574704712</v>
+        <v>4.705617717475642</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07748464615638764</v>
+        <v>0.07737948877801133</v>
       </c>
       <c r="C40">
-        <v>19.68820874357971</v>
+        <v>19.49788617108389</v>
       </c>
       <c r="D40">
-        <v>28.94280874357971</v>
+        <v>29.03918617108389</v>
       </c>
       <c r="E40">
-        <v>5.0246</v>
+        <v>5.3113</v>
       </c>
       <c r="F40">
-        <v>10.8946</v>
+        <v>11.1813</v>
       </c>
       <c r="G40">
         <v>1.64</v>
@@ -4549,28 +4549,28 @@
         <v>2.835</v>
       </c>
       <c r="M40">
-        <v>0.60247138</v>
+        <v>0.61832589</v>
       </c>
       <c r="N40">
-        <v>2.23252862</v>
+        <v>2.21667411</v>
       </c>
       <c r="O40">
-        <v>0.4911562964</v>
+        <v>0.4876683042</v>
       </c>
       <c r="P40">
-        <v>1.7413723236</v>
+        <v>1.7290058058</v>
       </c>
       <c r="Q40">
-        <v>2.8313723236</v>
+        <v>2.8190058058</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09853826799417362</v>
+        <v>0.0992741455377235</v>
       </c>
       <c r="T40">
-        <v>1.217973856678374</v>
+        <v>1.234968719116016</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.705617717475642</v>
+        <v>4.584960852924985</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07737948877801133</v>
+        <v>0.07805433139963502</v>
       </c>
       <c r="C41">
-        <v>19.49788617108389</v>
+        <v>18.60361256235814</v>
       </c>
       <c r="D41">
-        <v>29.03918617108389</v>
+        <v>28.43161256235814</v>
       </c>
       <c r="E41">
-        <v>5.3113</v>
+        <v>5.598000000000002</v>
       </c>
       <c r="F41">
-        <v>11.1813</v>
+        <v>11.468</v>
       </c>
       <c r="G41">
         <v>1.64</v>
@@ -4631,45 +4631,45 @@
         <v>2.835</v>
       </c>
       <c r="M41">
-        <v>0.61832589</v>
+        <v>0.6628504000000002</v>
       </c>
       <c r="N41">
-        <v>2.21667411</v>
+        <v>2.1721496</v>
       </c>
       <c r="O41">
-        <v>0.4876683042</v>
+        <v>0.477872912</v>
       </c>
       <c r="P41">
-        <v>1.7290058058</v>
+        <v>1.694276688</v>
       </c>
       <c r="Q41">
-        <v>2.8190058058</v>
+        <v>2.784276688</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0992741455377235</v>
+        <v>0.100034552332725</v>
       </c>
       <c r="T41">
-        <v>1.234968719116016</v>
+        <v>1.252530076968245</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.584960852924985</v>
+        <v>4.276983162414927</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07805433139963502</v>
+        <v>0.0779686740212587</v>
       </c>
       <c r="C42">
-        <v>18.60361256235814</v>
+        <v>18.39261905226485</v>
       </c>
       <c r="D42">
-        <v>28.43161256235814</v>
+        <v>28.50731905226485</v>
       </c>
       <c r="E42">
-        <v>5.598000000000002</v>
+        <v>5.884700000000001</v>
       </c>
       <c r="F42">
-        <v>11.468</v>
+        <v>11.7547</v>
       </c>
       <c r="G42">
         <v>1.64</v>
@@ -4713,28 +4713,28 @@
         <v>2.835</v>
       </c>
       <c r="M42">
-        <v>0.6628504000000002</v>
+        <v>0.6794216600000001</v>
       </c>
       <c r="N42">
-        <v>2.1721496</v>
+        <v>2.15557834</v>
       </c>
       <c r="O42">
-        <v>0.477872912</v>
+        <v>0.4742272348</v>
       </c>
       <c r="P42">
-        <v>1.694276688</v>
+        <v>1.6813511052</v>
       </c>
       <c r="Q42">
-        <v>2.784276688</v>
+        <v>2.7713511052</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.100034552332725</v>
+        <v>0.100820735629252</v>
       </c>
       <c r="T42">
-        <v>1.252530076968245</v>
+        <v>1.270686735086652</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.276983162414927</v>
+        <v>4.172666499917002</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0779686740212587</v>
+        <v>0.07788301664288239</v>
       </c>
       <c r="C43">
-        <v>18.39261905226485</v>
+        <v>18.18202979464718</v>
       </c>
       <c r="D43">
-        <v>28.50731905226485</v>
+        <v>28.58342979464718</v>
       </c>
       <c r="E43">
-        <v>5.884700000000001</v>
+        <v>6.171400000000001</v>
       </c>
       <c r="F43">
-        <v>11.7547</v>
+        <v>12.0414</v>
       </c>
       <c r="G43">
         <v>1.64</v>
@@ -4795,28 +4795,28 @@
         <v>2.835</v>
       </c>
       <c r="M43">
-        <v>0.6794216600000001</v>
+        <v>0.6959929200000001</v>
       </c>
       <c r="N43">
-        <v>2.15557834</v>
+        <v>2.13900708</v>
       </c>
       <c r="O43">
-        <v>0.4742272348</v>
+        <v>0.4705815576</v>
       </c>
       <c r="P43">
-        <v>1.6813511052</v>
+        <v>1.6684255224</v>
       </c>
       <c r="Q43">
-        <v>2.7713511052</v>
+        <v>2.7584255224</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.100820735629252</v>
+        <v>0.1016340286946248</v>
       </c>
       <c r="T43">
-        <v>1.270686735086652</v>
+        <v>1.289469484864314</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.172666499917002</v>
+        <v>4.073317297538026</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0778830166428824</v>
+        <v>0.07897125926450609</v>
       </c>
       <c r="C44">
-        <v>18.18202979464717</v>
+        <v>16.9575991427389</v>
       </c>
       <c r="D44">
-        <v>28.58342979464717</v>
+        <v>27.6456991427389</v>
       </c>
       <c r="E44">
-        <v>6.171399999999999</v>
+        <v>6.458100000000001</v>
       </c>
       <c r="F44">
-        <v>12.0414</v>
+        <v>12.3281</v>
       </c>
       <c r="G44">
         <v>1.64</v>
@@ -4877,45 +4877,45 @@
         <v>2.835</v>
       </c>
       <c r="M44">
-        <v>0.69599292</v>
+        <v>0.75571253</v>
       </c>
       <c r="N44">
-        <v>2.13900708</v>
+        <v>2.07928747</v>
       </c>
       <c r="O44">
-        <v>0.4705815576</v>
+        <v>0.4574432433999999</v>
       </c>
       <c r="P44">
-        <v>1.6684255224</v>
+        <v>1.6218442266</v>
       </c>
       <c r="Q44">
-        <v>2.7584255224</v>
+        <v>2.7118442266</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1016340286946248</v>
+        <v>0.1024758583587826</v>
       </c>
       <c r="T44">
-        <v>1.289469484864314</v>
+        <v>1.308911278493824</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.073317297538027</v>
+        <v>3.751426484883081</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07897125926450609</v>
+        <v>0.07891290188612979</v>
       </c>
       <c r="C45">
-        <v>16.9575991427389</v>
+        <v>16.71962125507137</v>
       </c>
       <c r="D45">
-        <v>27.6456991427389</v>
+        <v>27.69442125507137</v>
       </c>
       <c r="E45">
-        <v>6.458100000000001</v>
+        <v>6.744800000000001</v>
       </c>
       <c r="F45">
-        <v>12.3281</v>
+        <v>12.6148</v>
       </c>
       <c r="G45">
         <v>1.64</v>
@@ -4959,28 +4959,28 @@
         <v>2.835</v>
       </c>
       <c r="M45">
-        <v>0.75571253</v>
+        <v>0.77328724</v>
       </c>
       <c r="N45">
-        <v>2.07928747</v>
+        <v>2.06171276</v>
       </c>
       <c r="O45">
-        <v>0.4574432433999999</v>
+        <v>0.4535768072</v>
       </c>
       <c r="P45">
-        <v>1.6218442266</v>
+        <v>1.6081359528</v>
       </c>
       <c r="Q45">
-        <v>2.7118442266</v>
+        <v>2.6981359528</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1024758583587826</v>
+        <v>0.1033477533680889</v>
       </c>
       <c r="T45">
-        <v>1.308911278493824</v>
+        <v>1.329047421895817</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.751426484883081</v>
+        <v>3.666166792044829</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07891290188612979</v>
+        <v>0.07885454450775345</v>
       </c>
       <c r="C46">
-        <v>16.71962125507137</v>
+        <v>16.48181540394451</v>
       </c>
       <c r="D46">
-        <v>27.69442125507137</v>
+        <v>27.74331540394451</v>
       </c>
       <c r="E46">
-        <v>6.744800000000001</v>
+        <v>7.0315</v>
       </c>
       <c r="F46">
-        <v>12.6148</v>
+        <v>12.9015</v>
       </c>
       <c r="G46">
         <v>1.64</v>
@@ -5041,28 +5041,28 @@
         <v>2.835</v>
       </c>
       <c r="M46">
-        <v>0.77328724</v>
+        <v>0.79086195</v>
       </c>
       <c r="N46">
-        <v>2.06171276</v>
+        <v>2.04413805</v>
       </c>
       <c r="O46">
-        <v>0.4535768072</v>
+        <v>0.449710371</v>
       </c>
       <c r="P46">
-        <v>1.6081359528</v>
+        <v>1.594427679</v>
       </c>
       <c r="Q46">
-        <v>2.6981359528</v>
+        <v>2.684427679</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1033477533680889</v>
+        <v>0.1042513536504608</v>
       </c>
       <c r="T46">
-        <v>1.329047421895817</v>
+        <v>1.349915788694245</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.666166792044829</v>
+        <v>3.584696418888278</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07885454450775345</v>
+        <v>0.07879618712937715</v>
       </c>
       <c r="C47">
-        <v>16.48181540394451</v>
+        <v>16.24418250215476</v>
       </c>
       <c r="D47">
-        <v>27.74331540394451</v>
+        <v>27.79238250215476</v>
       </c>
       <c r="E47">
-        <v>7.0315</v>
+        <v>7.318200000000002</v>
       </c>
       <c r="F47">
-        <v>12.9015</v>
+        <v>13.1882</v>
       </c>
       <c r="G47">
         <v>1.64</v>
@@ -5123,28 +5123,28 @@
         <v>2.835</v>
       </c>
       <c r="M47">
-        <v>0.79086195</v>
+        <v>0.8084366600000001</v>
       </c>
       <c r="N47">
-        <v>2.04413805</v>
+        <v>2.02656334</v>
       </c>
       <c r="O47">
-        <v>0.449710371</v>
+        <v>0.4458439348</v>
       </c>
       <c r="P47">
-        <v>1.594427679</v>
+        <v>1.5807194052</v>
       </c>
       <c r="Q47">
-        <v>2.684427679</v>
+        <v>2.6707194052</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1042513536504608</v>
+        <v>0.1051884206099577</v>
       </c>
       <c r="T47">
-        <v>1.349915788694245</v>
+        <v>1.37155705796669</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.584696418888278</v>
+        <v>3.506768235868967</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07879618712937715</v>
+        <v>0.07976430975100084</v>
       </c>
       <c r="C48">
-        <v>16.24418250215476</v>
+        <v>15.16528521016176</v>
       </c>
       <c r="D48">
-        <v>27.79238250215476</v>
+        <v>27.00018521016176</v>
       </c>
       <c r="E48">
-        <v>7.318200000000002</v>
+        <v>7.604900000000002</v>
       </c>
       <c r="F48">
-        <v>13.1882</v>
+        <v>13.4749</v>
       </c>
       <c r="G48">
         <v>1.64</v>
@@ -5205,45 +5205,45 @@
         <v>2.835</v>
       </c>
       <c r="M48">
-        <v>0.8084366600000001</v>
+        <v>0.8637410900000002</v>
       </c>
       <c r="N48">
-        <v>2.02656334</v>
+        <v>1.97125891</v>
       </c>
       <c r="O48">
-        <v>0.4458439348</v>
+        <v>0.4336769602</v>
       </c>
       <c r="P48">
-        <v>1.5807194052</v>
+        <v>1.5375819498</v>
       </c>
       <c r="Q48">
-        <v>2.6707194052</v>
+        <v>2.6275819498</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1051884206099577</v>
+        <v>0.106160848586794</v>
       </c>
       <c r="T48">
-        <v>1.37155705796669</v>
+        <v>1.394014978909792</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.506768235868967</v>
+        <v>3.282233568394898</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07976430975100084</v>
+        <v>0.07972779237262453</v>
       </c>
       <c r="C49">
-        <v>15.16528521016176</v>
+        <v>14.90764622211093</v>
       </c>
       <c r="D49">
-        <v>27.00018521016176</v>
+        <v>27.02924622211093</v>
       </c>
       <c r="E49">
-        <v>7.604900000000002</v>
+        <v>7.891600000000001</v>
       </c>
       <c r="F49">
-        <v>13.4749</v>
+        <v>13.7616</v>
       </c>
       <c r="G49">
         <v>1.64</v>
@@ -5287,28 +5287,28 @@
         <v>2.835</v>
       </c>
       <c r="M49">
-        <v>0.8637410900000002</v>
+        <v>0.8821185600000001</v>
       </c>
       <c r="N49">
-        <v>1.97125891</v>
+        <v>1.95288144</v>
       </c>
       <c r="O49">
-        <v>0.4336769602</v>
+        <v>0.4296339168</v>
       </c>
       <c r="P49">
-        <v>1.5375819498</v>
+        <v>1.5232475232</v>
       </c>
       <c r="Q49">
-        <v>2.6275819498</v>
+        <v>2.6132475232</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.106160848586794</v>
+        <v>0.1071706776396625</v>
       </c>
       <c r="T49">
-        <v>1.394014978909792</v>
+        <v>1.417336666043015</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.282233568394898</v>
+        <v>3.213853702386672</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07972779237262452</v>
+        <v>0.07969127499424822</v>
       </c>
       <c r="C50">
-        <v>14.90764622211094</v>
+        <v>14.65006985973409</v>
       </c>
       <c r="D50">
-        <v>27.02924622211094</v>
+        <v>27.05836985973409</v>
       </c>
       <c r="E50">
-        <v>7.8916</v>
+        <v>8.1783</v>
       </c>
       <c r="F50">
-        <v>13.7616</v>
+        <v>14.0483</v>
       </c>
       <c r="G50">
         <v>1.64</v>
@@ -5369,28 +5369,28 @@
         <v>2.835</v>
       </c>
       <c r="M50">
-        <v>0.88211856</v>
+        <v>0.9004960300000001</v>
       </c>
       <c r="N50">
-        <v>1.95288144</v>
+        <v>1.93450397</v>
       </c>
       <c r="O50">
-        <v>0.4296339168</v>
+        <v>0.4255908734</v>
       </c>
       <c r="P50">
-        <v>1.5232475232</v>
+        <v>1.5089130966</v>
       </c>
       <c r="Q50">
-        <v>2.6132475232</v>
+        <v>2.5989130966</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1071706776396625</v>
+        <v>0.1082201078318592</v>
       </c>
       <c r="T50">
-        <v>1.417336666043014</v>
+        <v>1.441572929142245</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.213853702386673</v>
+        <v>3.148264851317556</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07969127499424822</v>
+        <v>0.0796547576158719</v>
       </c>
       <c r="C51">
-        <v>14.65006985973409</v>
+        <v>14.39255632568447</v>
       </c>
       <c r="D51">
-        <v>27.05836985973409</v>
+        <v>27.08755632568447</v>
       </c>
       <c r="E51">
-        <v>8.1783</v>
+        <v>8.465</v>
       </c>
       <c r="F51">
-        <v>14.0483</v>
+        <v>14.335</v>
       </c>
       <c r="G51">
         <v>1.64</v>
@@ -5451,28 +5451,28 @@
         <v>2.835</v>
       </c>
       <c r="M51">
-        <v>0.9004960300000001</v>
+        <v>0.9188735000000001</v>
       </c>
       <c r="N51">
-        <v>1.93450397</v>
+        <v>1.9161265</v>
       </c>
       <c r="O51">
-        <v>0.4255908734</v>
+        <v>0.42154783</v>
       </c>
       <c r="P51">
-        <v>1.5089130966</v>
+        <v>1.49457867</v>
       </c>
       <c r="Q51">
-        <v>2.5989130966</v>
+        <v>2.58457867</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1082201078318592</v>
+        <v>0.1093115152317438</v>
       </c>
       <c r="T51">
-        <v>1.441572929142245</v>
+        <v>1.466778642765445</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.148264851317556</v>
+        <v>3.085299554291205</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0796547576158719</v>
+        <v>0.07961824023749559</v>
       </c>
       <c r="C52">
-        <v>14.39255632568447</v>
+        <v>14.13510582349064</v>
       </c>
       <c r="D52">
-        <v>27.08755632568447</v>
+        <v>27.11680582349064</v>
       </c>
       <c r="E52">
-        <v>8.465</v>
+        <v>8.7517</v>
       </c>
       <c r="F52">
-        <v>14.335</v>
+        <v>14.6217</v>
       </c>
       <c r="G52">
         <v>1.64</v>
@@ -5533,28 +5533,28 @@
         <v>2.835</v>
       </c>
       <c r="M52">
-        <v>0.9188735000000001</v>
+        <v>0.9372509700000001</v>
       </c>
       <c r="N52">
-        <v>1.9161265</v>
+        <v>1.89774903</v>
       </c>
       <c r="O52">
-        <v>0.42154783</v>
+        <v>0.4175047866</v>
       </c>
       <c r="P52">
-        <v>1.49457867</v>
+        <v>1.4802442434</v>
       </c>
       <c r="Q52">
-        <v>2.58457867</v>
+        <v>2.5702442434</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1093115152317438</v>
+        <v>0.11044746987244</v>
       </c>
       <c r="T52">
-        <v>1.466778642765445</v>
+        <v>1.493013161026327</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.085299554291205</v>
+        <v>3.024803484599221</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07961824023749559</v>
+        <v>0.08274540285911927</v>
       </c>
       <c r="C53">
-        <v>14.13510582349064</v>
+        <v>11.55316324859159</v>
       </c>
       <c r="D53">
-        <v>27.11680582349064</v>
+        <v>24.82156324859159</v>
       </c>
       <c r="E53">
-        <v>8.7517</v>
+        <v>9.038400000000003</v>
       </c>
       <c r="F53">
-        <v>14.6217</v>
+        <v>14.9084</v>
       </c>
       <c r="G53">
         <v>1.64</v>
@@ -5615,45 +5615,45 @@
         <v>2.835</v>
       </c>
       <c r="M53">
-        <v>0.9372509700000001</v>
+        <v>1.07191396</v>
       </c>
       <c r="N53">
-        <v>1.89774903</v>
+        <v>1.76308604</v>
       </c>
       <c r="O53">
-        <v>0.4175047866</v>
+        <v>0.3878789287999999</v>
       </c>
       <c r="P53">
-        <v>1.4802442434</v>
+        <v>1.3752071112</v>
       </c>
       <c r="Q53">
-        <v>2.5702442434</v>
+        <v>2.4652071112</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.11044746987244</v>
+        <v>0.1116307559564985</v>
       </c>
       <c r="T53">
-        <v>1.493013161026327</v>
+        <v>1.520340784214745</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.024803484599221</v>
+        <v>2.644801827191428</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08274540285911927</v>
+        <v>0.08276972548074296</v>
       </c>
       <c r="C54">
-        <v>11.55316324859159</v>
+        <v>11.2501329815108</v>
       </c>
       <c r="D54">
-        <v>24.82156324859159</v>
+        <v>24.8052329815108</v>
       </c>
       <c r="E54">
-        <v>9.038400000000003</v>
+        <v>9.325100000000003</v>
       </c>
       <c r="F54">
-        <v>14.9084</v>
+        <v>15.1951</v>
       </c>
       <c r="G54">
         <v>1.64</v>
@@ -5697,28 +5697,28 @@
         <v>2.835</v>
       </c>
       <c r="M54">
-        <v>1.07191396</v>
+        <v>1.09252769</v>
       </c>
       <c r="N54">
-        <v>1.76308604</v>
+        <v>1.74247231</v>
       </c>
       <c r="O54">
-        <v>0.3878789287999999</v>
+        <v>0.3833439081999999</v>
       </c>
       <c r="P54">
-        <v>1.3752071112</v>
+        <v>1.3591284018</v>
       </c>
       <c r="Q54">
-        <v>2.4652071112</v>
+        <v>2.4491284018</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1116307559564985</v>
+        <v>0.1128643946398786</v>
       </c>
       <c r="T54">
-        <v>1.520340784214745</v>
+        <v>1.54883128498565</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.644801827191428</v>
+        <v>2.594899905923665</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08276972548074296</v>
+        <v>0.08279404810236664</v>
       </c>
       <c r="C55">
-        <v>11.2501329815108</v>
+        <v>10.94712418787927</v>
       </c>
       <c r="D55">
-        <v>24.8052329815108</v>
+        <v>24.78892418787927</v>
       </c>
       <c r="E55">
-        <v>9.325100000000003</v>
+        <v>9.611800000000002</v>
       </c>
       <c r="F55">
-        <v>15.1951</v>
+        <v>15.4818</v>
       </c>
       <c r="G55">
         <v>1.64</v>
@@ -5779,28 +5779,28 @@
         <v>2.835</v>
       </c>
       <c r="M55">
-        <v>1.09252769</v>
+        <v>1.11314142</v>
       </c>
       <c r="N55">
-        <v>1.74247231</v>
+        <v>1.72185858</v>
       </c>
       <c r="O55">
-        <v>0.3833439081999999</v>
+        <v>0.3788088875999999</v>
       </c>
       <c r="P55">
-        <v>1.3591284018</v>
+        <v>1.3430496924</v>
       </c>
       <c r="Q55">
-        <v>2.4491284018</v>
+        <v>2.4330496924</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1128643946398786</v>
+        <v>0.1141516697877536</v>
       </c>
       <c r="T55">
-        <v>1.54883128498565</v>
+        <v>1.578560503181376</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.594899905923665</v>
+        <v>2.546846203962116</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08279404810236664</v>
+        <v>0.08281837072399034</v>
       </c>
       <c r="C56">
-        <v>10.94712418787927</v>
+        <v>10.6441368253701</v>
       </c>
       <c r="D56">
-        <v>24.78892418787927</v>
+        <v>24.7726368253701</v>
       </c>
       <c r="E56">
-        <v>9.611800000000002</v>
+        <v>9.898500000000002</v>
       </c>
       <c r="F56">
-        <v>15.4818</v>
+        <v>15.7685</v>
       </c>
       <c r="G56">
         <v>1.64</v>
@@ -5861,28 +5861,28 @@
         <v>2.835</v>
       </c>
       <c r="M56">
-        <v>1.11314142</v>
+        <v>1.13375515</v>
       </c>
       <c r="N56">
-        <v>1.72185858</v>
+        <v>1.70124485</v>
       </c>
       <c r="O56">
-        <v>0.3788088875999999</v>
+        <v>0.3742738669999999</v>
       </c>
       <c r="P56">
-        <v>1.3430496924</v>
+        <v>1.326970983</v>
       </c>
       <c r="Q56">
-        <v>2.4330496924</v>
+        <v>2.416970983</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1141516697877536</v>
+        <v>0.115496157164423</v>
       </c>
       <c r="T56">
-        <v>1.578560503181376</v>
+        <v>1.609611019963579</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.546846203962116</v>
+        <v>2.500539909344623</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08281837072399034</v>
+        <v>0.08454621334561402</v>
       </c>
       <c r="C57">
-        <v>10.6441368253701</v>
+        <v>9.252729705345843</v>
       </c>
       <c r="D57">
-        <v>24.7726368253701</v>
+        <v>23.66792970534584</v>
       </c>
       <c r="E57">
-        <v>9.898500000000002</v>
+        <v>10.1852</v>
       </c>
       <c r="F57">
-        <v>15.7685</v>
+        <v>16.0552</v>
       </c>
       <c r="G57">
         <v>1.64</v>
@@ -5943,45 +5943,45 @@
         <v>2.835</v>
       </c>
       <c r="M57">
-        <v>1.13375515</v>
+        <v>1.21698416</v>
       </c>
       <c r="N57">
-        <v>1.70124485</v>
+        <v>1.61801584</v>
       </c>
       <c r="O57">
-        <v>0.3742738669999999</v>
+        <v>0.3559634848</v>
       </c>
       <c r="P57">
-        <v>1.326970983</v>
+        <v>1.2620523552</v>
       </c>
       <c r="Q57">
-        <v>2.416970983</v>
+        <v>2.3520523552</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.115496157164423</v>
+        <v>0.1169017576036682</v>
       </c>
       <c r="T57">
-        <v>1.609611019963579</v>
+        <v>1.642072923872245</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.500539909344623</v>
+        <v>2.329529087708093</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08454621334561402</v>
+        <v>0.08460095596723771</v>
       </c>
       <c r="C58">
-        <v>9.252729705345843</v>
+        <v>8.932637628058625</v>
       </c>
       <c r="D58">
-        <v>23.66792970534584</v>
+        <v>23.63453762805863</v>
       </c>
       <c r="E58">
-        <v>10.1852</v>
+        <v>10.4719</v>
       </c>
       <c r="F58">
-        <v>16.0552</v>
+        <v>16.3419</v>
       </c>
       <c r="G58">
         <v>1.64</v>
@@ -6025,28 +6025,28 @@
         <v>2.835</v>
       </c>
       <c r="M58">
-        <v>1.21698416</v>
+        <v>1.23871602</v>
       </c>
       <c r="N58">
-        <v>1.61801584</v>
+        <v>1.59628398</v>
       </c>
       <c r="O58">
-        <v>0.3559634848</v>
+        <v>0.3511824755999999</v>
       </c>
       <c r="P58">
-        <v>1.2620523552</v>
+        <v>1.2451015044</v>
       </c>
       <c r="Q58">
-        <v>2.3520523552</v>
+        <v>2.3351015044</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1169017576036682</v>
+        <v>0.1183727348075296</v>
       </c>
       <c r="T58">
-        <v>1.642072923872245</v>
+        <v>1.676044683776664</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.329529087708093</v>
+        <v>2.288660156344793</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08460095596723771</v>
+        <v>0.08465569858886141</v>
       </c>
       <c r="C59">
-        <v>8.932637628058625</v>
+        <v>8.612639640952182</v>
       </c>
       <c r="D59">
-        <v>23.63453762805863</v>
+        <v>23.60123964095218</v>
       </c>
       <c r="E59">
-        <v>10.4719</v>
+        <v>10.7586</v>
       </c>
       <c r="F59">
-        <v>16.3419</v>
+        <v>16.6286</v>
       </c>
       <c r="G59">
         <v>1.64</v>
@@ -6107,28 +6107,28 @@
         <v>2.835</v>
       </c>
       <c r="M59">
-        <v>1.23871602</v>
+        <v>1.26044788</v>
       </c>
       <c r="N59">
-        <v>1.59628398</v>
+        <v>1.57455212</v>
       </c>
       <c r="O59">
-        <v>0.3511824755999999</v>
+        <v>0.3464014663999999</v>
       </c>
       <c r="P59">
-        <v>1.2451015044</v>
+        <v>1.2281506536</v>
       </c>
       <c r="Q59">
-        <v>2.3351015044</v>
+        <v>2.3181506536</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1183727348075296</v>
+        <v>0.1199137585449081</v>
       </c>
       <c r="T59">
-        <v>1.676044683776664</v>
+        <v>1.711634146533674</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.288660156344793</v>
+        <v>2.249200498476779</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08465569858886141</v>
+        <v>0.08471044121048507</v>
       </c>
       <c r="C60">
-        <v>8.612639640952185</v>
+        <v>8.292735346903576</v>
       </c>
       <c r="D60">
-        <v>23.60123964095218</v>
+        <v>23.56803534690357</v>
       </c>
       <c r="E60">
-        <v>10.7586</v>
+        <v>11.0453</v>
       </c>
       <c r="F60">
-        <v>16.6286</v>
+        <v>16.9153</v>
       </c>
       <c r="G60">
         <v>1.64</v>
@@ -6189,28 +6189,28 @@
         <v>2.835</v>
       </c>
       <c r="M60">
-        <v>1.26044788</v>
+        <v>1.28217974</v>
       </c>
       <c r="N60">
-        <v>1.57455212</v>
+        <v>1.55282026</v>
       </c>
       <c r="O60">
-        <v>0.3464014664</v>
+        <v>0.3416204572</v>
       </c>
       <c r="P60">
-        <v>1.2281506536</v>
+        <v>1.2111998028</v>
       </c>
       <c r="Q60">
-        <v>2.3181506536</v>
+        <v>2.3011998028</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1199137585449081</v>
+        <v>0.1215299541719148</v>
       </c>
       <c r="T60">
-        <v>1.711634146533674</v>
+        <v>1.748959680644684</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.249200498476779</v>
+        <v>2.211078456129716</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08471044121048507</v>
+        <v>0.08476518383210876</v>
       </c>
       <c r="C61">
-        <v>8.292735346903576</v>
+        <v>7.972924351021494</v>
       </c>
       <c r="D61">
-        <v>23.56803534690357</v>
+        <v>23.53492435102149</v>
       </c>
       <c r="E61">
-        <v>11.0453</v>
+        <v>11.332</v>
       </c>
       <c r="F61">
-        <v>16.9153</v>
+        <v>17.202</v>
       </c>
       <c r="G61">
         <v>1.64</v>
@@ -6271,28 +6271,28 @@
         <v>2.835</v>
       </c>
       <c r="M61">
-        <v>1.28217974</v>
+        <v>1.3039116</v>
       </c>
       <c r="N61">
-        <v>1.55282026</v>
+        <v>1.5310884</v>
       </c>
       <c r="O61">
-        <v>0.3416204572</v>
+        <v>0.3368394479999999</v>
       </c>
       <c r="P61">
-        <v>1.2111998028</v>
+        <v>1.194248952</v>
       </c>
       <c r="Q61">
-        <v>2.3011998028</v>
+        <v>2.284248952</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1215299541719148</v>
+        <v>0.1232269595802719</v>
       </c>
       <c r="T61">
-        <v>1.748959680644684</v>
+        <v>1.788151491461245</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.211078456129716</v>
+        <v>2.174227148527553</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08476518383210876</v>
+        <v>0.08481992645373246</v>
       </c>
       <c r="C62">
-        <v>7.972924351021494</v>
+        <v>7.653206260630732</v>
       </c>
       <c r="D62">
-        <v>23.53492435102149</v>
+        <v>23.50190626063073</v>
       </c>
       <c r="E62">
-        <v>11.332</v>
+        <v>11.6187</v>
       </c>
       <c r="F62">
-        <v>17.202</v>
+        <v>17.4887</v>
       </c>
       <c r="G62">
         <v>1.64</v>
@@ -6353,28 +6353,28 @@
         <v>2.835</v>
       </c>
       <c r="M62">
-        <v>1.3039116</v>
+        <v>1.32564346</v>
       </c>
       <c r="N62">
-        <v>1.5310884</v>
+        <v>1.50935654</v>
       </c>
       <c r="O62">
-        <v>0.3368394479999999</v>
+        <v>0.3320584388</v>
       </c>
       <c r="P62">
-        <v>1.194248952</v>
+        <v>1.1772981012</v>
       </c>
       <c r="Q62">
-        <v>2.284248952</v>
+        <v>2.2672981012</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1232269595802719</v>
+        <v>0.1250109909070063</v>
       </c>
       <c r="T62">
-        <v>1.788151491461245</v>
+        <v>1.829353138729937</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.174227148527553</v>
+        <v>2.138584080518905</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08481992645373246</v>
+        <v>0.08487466907535615</v>
       </c>
       <c r="C63">
-        <v>7.653206260630732</v>
+        <v>7.333580685256567</v>
       </c>
       <c r="D63">
-        <v>23.50190626063073</v>
+        <v>23.46898068525657</v>
       </c>
       <c r="E63">
-        <v>11.6187</v>
+        <v>11.9054</v>
       </c>
       <c r="F63">
-        <v>17.4887</v>
+        <v>17.7754</v>
       </c>
       <c r="G63">
         <v>1.64</v>
@@ -6435,28 +6435,28 @@
         <v>2.835</v>
       </c>
       <c r="M63">
-        <v>1.32564346</v>
+        <v>1.34737532</v>
       </c>
       <c r="N63">
-        <v>1.50935654</v>
+        <v>1.48762468</v>
       </c>
       <c r="O63">
-        <v>0.3320584388</v>
+        <v>0.3272774295999999</v>
       </c>
       <c r="P63">
-        <v>1.1772981012</v>
+        <v>1.1603472504</v>
       </c>
       <c r="Q63">
-        <v>2.2672981012</v>
+        <v>2.2503472504</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1250109909070063</v>
+        <v>0.1268889186193583</v>
       </c>
       <c r="T63">
-        <v>1.829353138729937</v>
+        <v>1.872723293749613</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.138584080518905</v>
+        <v>2.104090788897632</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08487466907535615</v>
+        <v>0.08492941169697985</v>
       </c>
       <c r="C64">
-        <v>7.333580685256567</v>
+        <v>7.014047236609397</v>
       </c>
       <c r="D64">
-        <v>23.46898068525657</v>
+        <v>23.4361472366094</v>
       </c>
       <c r="E64">
-        <v>11.9054</v>
+        <v>12.1921</v>
       </c>
       <c r="F64">
-        <v>17.7754</v>
+        <v>18.0621</v>
       </c>
       <c r="G64">
         <v>1.64</v>
@@ -6517,28 +6517,28 @@
         <v>2.835</v>
       </c>
       <c r="M64">
-        <v>1.34737532</v>
+        <v>1.36910718</v>
       </c>
       <c r="N64">
-        <v>1.48762468</v>
+        <v>1.46589282</v>
       </c>
       <c r="O64">
-        <v>0.3272774295999999</v>
+        <v>0.3224964204</v>
       </c>
       <c r="P64">
-        <v>1.1603472504</v>
+        <v>1.1433963996</v>
       </c>
       <c r="Q64">
-        <v>2.2503472504</v>
+        <v>2.2333963996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1268889186193583</v>
+        <v>0.1288683559377833</v>
       </c>
       <c r="T64">
-        <v>1.872723293749613</v>
+        <v>1.918437781473056</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.104090788897632</v>
+        <v>2.070692522407194</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08492941169697985</v>
+        <v>0.08498415431860352</v>
       </c>
       <c r="C65">
-        <v>7.014047236609397</v>
+        <v>6.694605528569486</v>
       </c>
       <c r="D65">
-        <v>23.4361472366094</v>
+        <v>23.40340552856949</v>
       </c>
       <c r="E65">
-        <v>12.1921</v>
+        <v>12.4788</v>
       </c>
       <c r="F65">
-        <v>18.0621</v>
+        <v>18.3488</v>
       </c>
       <c r="G65">
         <v>1.64</v>
@@ -6599,28 +6599,28 @@
         <v>2.835</v>
       </c>
       <c r="M65">
-        <v>1.36910718</v>
+        <v>1.39083904</v>
       </c>
       <c r="N65">
-        <v>1.46589282</v>
+        <v>1.44416096</v>
       </c>
       <c r="O65">
-        <v>0.3224964204</v>
+        <v>0.3177154112</v>
       </c>
       <c r="P65">
-        <v>1.1433963996</v>
+        <v>1.1264455488</v>
       </c>
       <c r="Q65">
-        <v>2.2333963996</v>
+        <v>2.2164455488</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1288683559377833</v>
+        <v>0.1309577619961209</v>
       </c>
       <c r="T65">
-        <v>1.918437781473056</v>
+        <v>1.966691962958912</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.070692522407194</v>
+        <v>2.038337951744581</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08498415431860352</v>
+        <v>0.08503889694022722</v>
       </c>
       <c r="C66">
-        <v>6.694605528569486</v>
+        <v>6.375255177171791</v>
       </c>
       <c r="D66">
-        <v>23.40340552856949</v>
+        <v>23.37075517717179</v>
       </c>
       <c r="E66">
-        <v>12.4788</v>
+        <v>12.7655</v>
       </c>
       <c r="F66">
-        <v>18.3488</v>
+        <v>18.6355</v>
       </c>
       <c r="G66">
         <v>1.64</v>
@@ -6681,28 +6681,28 @@
         <v>2.835</v>
       </c>
       <c r="M66">
-        <v>1.39083904</v>
+        <v>1.4125709</v>
       </c>
       <c r="N66">
-        <v>1.44416096</v>
+        <v>1.4224291</v>
       </c>
       <c r="O66">
-        <v>0.3177154112</v>
+        <v>0.3129344019999999</v>
       </c>
       <c r="P66">
-        <v>1.1264455488</v>
+        <v>1.109494698</v>
       </c>
       <c r="Q66">
-        <v>2.2164455488</v>
+        <v>2.199494698</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1309577619961209</v>
+        <v>0.1331665626863635</v>
       </c>
       <c r="T66">
-        <v>1.966691962958912</v>
+        <v>2.01770352624396</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.038337951744581</v>
+        <v>2.006978906333126</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08503889694022722</v>
+        <v>0.09240379956185088</v>
       </c>
       <c r="C67">
-        <v>6.375255177171791</v>
+        <v>2.39522249417367</v>
       </c>
       <c r="D67">
-        <v>23.37075517717179</v>
+        <v>19.67742249417367</v>
       </c>
       <c r="E67">
-        <v>12.7655</v>
+        <v>13.0522</v>
       </c>
       <c r="F67">
-        <v>18.6355</v>
+        <v>18.9222</v>
       </c>
       <c r="G67">
         <v>1.64</v>
@@ -6763,45 +6763,45 @@
         <v>2.835</v>
       </c>
       <c r="M67">
-        <v>1.4125709</v>
+        <v>1.702998</v>
       </c>
       <c r="N67">
-        <v>1.4224291</v>
+        <v>1.132002</v>
       </c>
       <c r="O67">
-        <v>0.3129344019999999</v>
+        <v>0.2490404399999999</v>
       </c>
       <c r="P67">
-        <v>1.109494698</v>
+        <v>0.8829615599999998</v>
       </c>
       <c r="Q67">
-        <v>2.199494698</v>
+        <v>1.97296156</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1331665626863635</v>
+        <v>0.1355052928289732</v>
       </c>
       <c r="T67">
-        <v>2.01770352624396</v>
+        <v>2.071715769722245</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.006978906333126</v>
+        <v>1.664711291498874</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09240379956185088</v>
+        <v>0.09256930218347459</v>
       </c>
       <c r="C68">
-        <v>2.39522249417367</v>
+        <v>2.038889960491481</v>
       </c>
       <c r="D68">
-        <v>19.67742249417367</v>
+        <v>19.60778996049148</v>
       </c>
       <c r="E68">
-        <v>13.0522</v>
+        <v>13.3389</v>
       </c>
       <c r="F68">
-        <v>18.9222</v>
+        <v>19.2089</v>
       </c>
       <c r="G68">
         <v>1.64</v>
@@ -6845,28 +6845,28 @@
         <v>2.835</v>
       </c>
       <c r="M68">
-        <v>1.702998</v>
+        <v>1.728801</v>
       </c>
       <c r="N68">
-        <v>1.132002</v>
+        <v>1.106199</v>
       </c>
       <c r="O68">
-        <v>0.2490404399999999</v>
+        <v>0.2433637799999999</v>
       </c>
       <c r="P68">
-        <v>0.8829615599999998</v>
+        <v>0.8628352199999998</v>
       </c>
       <c r="Q68">
-        <v>1.97296156</v>
+        <v>1.95283522</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1355052928289732</v>
+        <v>0.1379857641923472</v>
       </c>
       <c r="T68">
-        <v>2.071715769722245</v>
+        <v>2.129001482502245</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.664711291498874</v>
+        <v>1.639864854312324</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09256930218347459</v>
+        <v>0.09273480480509827</v>
       </c>
       <c r="C69">
-        <v>2.038889960491481</v>
+        <v>1.683048506592108</v>
       </c>
       <c r="D69">
-        <v>19.60778996049148</v>
+        <v>19.53864850659211</v>
       </c>
       <c r="E69">
-        <v>13.3389</v>
+        <v>13.6256</v>
       </c>
       <c r="F69">
-        <v>19.2089</v>
+        <v>19.4956</v>
       </c>
       <c r="G69">
         <v>1.64</v>
@@ -6927,28 +6927,28 @@
         <v>2.835</v>
       </c>
       <c r="M69">
-        <v>1.728801</v>
+        <v>1.754604</v>
       </c>
       <c r="N69">
-        <v>1.106199</v>
+        <v>1.080396</v>
       </c>
       <c r="O69">
-        <v>0.2433637799999999</v>
+        <v>0.2376871199999999</v>
       </c>
       <c r="P69">
-        <v>0.8628352199999998</v>
+        <v>0.8427088799999998</v>
       </c>
       <c r="Q69">
-        <v>1.95283522</v>
+        <v>1.93270888</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1379857641923472</v>
+        <v>0.1406212650159321</v>
       </c>
       <c r="T69">
-        <v>2.129001482502245</v>
+        <v>2.189867552330995</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.639864854312324</v>
+        <v>1.615749194690084</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09273480480509827</v>
+        <v>0.09290030742672195</v>
       </c>
       <c r="C70">
-        <v>1.683048506592108</v>
+        <v>1.327692955758273</v>
       </c>
       <c r="D70">
-        <v>19.53864850659211</v>
+        <v>19.46999295575828</v>
       </c>
       <c r="E70">
-        <v>13.6256</v>
+        <v>13.9123</v>
       </c>
       <c r="F70">
-        <v>19.4956</v>
+        <v>19.7823</v>
       </c>
       <c r="G70">
         <v>1.64</v>
@@ -7009,28 +7009,28 @@
         <v>2.835</v>
       </c>
       <c r="M70">
-        <v>1.754604</v>
+        <v>1.780407</v>
       </c>
       <c r="N70">
-        <v>1.080396</v>
+        <v>1.054593</v>
       </c>
       <c r="O70">
-        <v>0.2376871199999999</v>
+        <v>0.2320104599999999</v>
       </c>
       <c r="P70">
-        <v>0.8427088799999998</v>
+        <v>0.8225825399999998</v>
       </c>
       <c r="Q70">
-        <v>1.93270888</v>
+        <v>1.91258254</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1406212650159321</v>
+        <v>0.143426798150716</v>
       </c>
       <c r="T70">
-        <v>2.189867552330995</v>
+        <v>2.254660465374503</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.615749194690084</v>
+        <v>1.592332539694575</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09290030742672195</v>
+        <v>0.09306581004834563</v>
       </c>
       <c r="C71">
-        <v>1.327692955758273</v>
+        <v>0.9728182037784237</v>
       </c>
       <c r="D71">
-        <v>19.46999295575828</v>
+        <v>19.40181820377843</v>
       </c>
       <c r="E71">
-        <v>13.9123</v>
+        <v>14.199</v>
       </c>
       <c r="F71">
-        <v>19.7823</v>
+        <v>20.069</v>
       </c>
       <c r="G71">
         <v>1.64</v>
@@ -7091,28 +7091,28 @@
         <v>2.835</v>
       </c>
       <c r="M71">
-        <v>1.780407</v>
+        <v>1.80621</v>
       </c>
       <c r="N71">
-        <v>1.054593</v>
+        <v>1.02879</v>
       </c>
       <c r="O71">
-        <v>0.2320104599999999</v>
+        <v>0.2263338</v>
       </c>
       <c r="P71">
-        <v>0.8225825399999998</v>
+        <v>0.8024562</v>
       </c>
       <c r="Q71">
-        <v>1.91258254</v>
+        <v>1.8924562</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.143426798150716</v>
+        <v>0.1464193668278188</v>
       </c>
       <c r="T71">
-        <v>2.254660465374503</v>
+        <v>2.323772905954245</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.592332539694575</v>
+        <v>1.569584931984653</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09306581004834563</v>
+        <v>0.09323131266996934</v>
       </c>
       <c r="C72">
-        <v>0.9728182037784237</v>
+        <v>0.6184192176817369</v>
       </c>
       <c r="D72">
-        <v>19.40181820377843</v>
+        <v>19.33411921768174</v>
       </c>
       <c r="E72">
-        <v>14.199</v>
+        <v>14.4857</v>
       </c>
       <c r="F72">
-        <v>20.069</v>
+        <v>20.3557</v>
       </c>
       <c r="G72">
         <v>1.64</v>
@@ -7173,28 +7173,28 @@
         <v>2.835</v>
       </c>
       <c r="M72">
-        <v>1.80621</v>
+        <v>1.832013</v>
       </c>
       <c r="N72">
-        <v>1.02879</v>
+        <v>1.002987</v>
       </c>
       <c r="O72">
-        <v>0.2263338</v>
+        <v>0.22065714</v>
       </c>
       <c r="P72">
-        <v>0.8024562</v>
+        <v>0.7823298599999999</v>
       </c>
       <c r="Q72">
-        <v>1.8924562</v>
+        <v>1.87232986</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1464193668278188</v>
+        <v>0.1496183195516184</v>
       </c>
       <c r="T72">
-        <v>2.323772905954245</v>
+        <v>2.397651721746383</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.569584931984653</v>
+        <v>1.5474781019567</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09323131266996933</v>
+        <v>0.09339681529159302</v>
       </c>
       <c r="C73">
-        <v>0.6184192176817476</v>
+        <v>0.2644910344995672</v>
       </c>
       <c r="D73">
-        <v>19.33411921768175</v>
+        <v>19.26689103449957</v>
       </c>
       <c r="E73">
-        <v>14.4857</v>
+        <v>14.7724</v>
       </c>
       <c r="F73">
-        <v>20.3557</v>
+        <v>20.6424</v>
       </c>
       <c r="G73">
         <v>1.64</v>
@@ -7255,28 +7255,28 @@
         <v>2.835</v>
       </c>
       <c r="M73">
-        <v>1.832013</v>
+        <v>1.857816</v>
       </c>
       <c r="N73">
-        <v>1.002987</v>
+        <v>0.9771839999999998</v>
       </c>
       <c r="O73">
-        <v>0.22065714</v>
+        <v>0.21498048</v>
       </c>
       <c r="P73">
-        <v>0.78232986</v>
+        <v>0.7622035199999999</v>
       </c>
       <c r="Q73">
-        <v>1.87232986</v>
+        <v>1.85220352</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1496183195516184</v>
+        <v>0.1530457688985465</v>
       </c>
       <c r="T73">
-        <v>2.397651721746382</v>
+        <v>2.476807595809388</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.5474781019567</v>
+        <v>1.525985350540635</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09339681529159302</v>
+        <v>0.0935623179132167</v>
       </c>
       <c r="C74">
-        <v>0.2644910344995672</v>
+        <v>-0.08897123994744049</v>
       </c>
       <c r="D74">
-        <v>19.26689103449957</v>
+        <v>19.20012876005256</v>
       </c>
       <c r="E74">
-        <v>14.7724</v>
+        <v>15.0591</v>
       </c>
       <c r="F74">
-        <v>20.6424</v>
+        <v>20.9291</v>
       </c>
       <c r="G74">
         <v>1.64</v>
@@ -7337,28 +7337,28 @@
         <v>2.835</v>
       </c>
       <c r="M74">
-        <v>1.857816</v>
+        <v>1.883619</v>
       </c>
       <c r="N74">
-        <v>0.9771839999999998</v>
+        <v>0.9513809999999998</v>
       </c>
       <c r="O74">
-        <v>0.21498048</v>
+        <v>0.2093038199999999</v>
       </c>
       <c r="P74">
-        <v>0.7622035199999999</v>
+        <v>0.7420771799999999</v>
       </c>
       <c r="Q74">
-        <v>1.85220352</v>
+        <v>1.83207718</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1530457688985465</v>
+        <v>0.1567271033822841</v>
       </c>
       <c r="T74">
-        <v>2.476807595809388</v>
+        <v>2.561826867951133</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.525985350540635</v>
+        <v>1.505081441629119</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0935623179132167</v>
+        <v>0.1291786296192844</v>
       </c>
       <c r="C75">
-        <v>-0.08897123994744049</v>
+        <v>-8.577266466891587</v>
       </c>
       <c r="D75">
-        <v>19.20012876005256</v>
+        <v>10.99853353310841</v>
       </c>
       <c r="E75">
-        <v>15.0591</v>
+        <v>15.3458</v>
       </c>
       <c r="F75">
-        <v>20.9291</v>
+        <v>21.2158</v>
       </c>
       <c r="G75">
         <v>1.64</v>
@@ -7419,45 +7419,45 @@
         <v>2.835</v>
       </c>
       <c r="M75">
-        <v>1.883619</v>
+        <v>3.114479440000001</v>
       </c>
       <c r="N75">
-        <v>0.9513809999999998</v>
+        <v>-0.2794794400000007</v>
       </c>
       <c r="O75">
-        <v>0.2093038199999999</v>
+        <v>-0.06148547680000015</v>
       </c>
       <c r="P75">
-        <v>0.7420771799999999</v>
+        <v>-0.2179939632000005</v>
       </c>
       <c r="Q75">
-        <v>1.83207718</v>
+        <v>0.8720060367999996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1567271033822841</v>
+        <v>0.1626964491407371</v>
       </c>
       <c r="T75">
-        <v>2.561826867951133</v>
+        <v>2.699687047130185</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.22</v>
+        <v>0.2002581850403867</v>
       </c>
       <c r="W75">
-        <v>0.0702</v>
+        <v>0.1174020984360713</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.505081441629119</v>
+        <v>0.910264477456303</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1291786296192844</v>
+        <v>0.1301886296192844</v>
       </c>
       <c r="C76">
-        <v>-8.577266466891587</v>
+        <v>-8.995601722951024</v>
       </c>
       <c r="D76">
-        <v>10.99853353310841</v>
+        <v>10.86689827704898</v>
       </c>
       <c r="E76">
-        <v>15.3458</v>
+        <v>15.6325</v>
       </c>
       <c r="F76">
-        <v>21.2158</v>
+        <v>21.5025</v>
       </c>
       <c r="G76">
         <v>1.64</v>
@@ -7501,37 +7501,37 @@
         <v>2.835</v>
       </c>
       <c r="M76">
-        <v>3.114479440000001</v>
+        <v>3.156567</v>
       </c>
       <c r="N76">
-        <v>-0.2794794400000007</v>
+        <v>-0.3215670000000004</v>
       </c>
       <c r="O76">
-        <v>-0.06148547680000015</v>
+        <v>-0.07074474000000008</v>
       </c>
       <c r="P76">
-        <v>-0.2179939632000005</v>
+        <v>-0.2508222600000003</v>
       </c>
       <c r="Q76">
-        <v>0.8720060367999996</v>
+        <v>0.8391777399999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1626964491407371</v>
+        <v>0.1673723071063666</v>
       </c>
       <c r="T76">
-        <v>2.699687047130185</v>
+        <v>2.807674529015393</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2002581850403867</v>
+        <v>0.1975880759065149</v>
       </c>
       <c r="W76">
-        <v>0.1174020984360713</v>
+        <v>0.1177940704569236</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.910264477456303</v>
+        <v>0.8981276177568858</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1301886296192844</v>
+        <v>0.1311986296192844</v>
       </c>
       <c r="C77">
-        <v>-8.995601722951024</v>
+        <v>-9.410823308235818</v>
       </c>
       <c r="D77">
-        <v>10.86689827704898</v>
+        <v>10.73837669176418</v>
       </c>
       <c r="E77">
-        <v>15.6325</v>
+        <v>15.9192</v>
       </c>
       <c r="F77">
-        <v>21.5025</v>
+        <v>21.7892</v>
       </c>
       <c r="G77">
         <v>1.64</v>
@@ -7583,37 +7583,37 @@
         <v>2.835</v>
       </c>
       <c r="M77">
-        <v>3.156567</v>
+        <v>3.19865456</v>
       </c>
       <c r="N77">
-        <v>-0.3215670000000004</v>
+        <v>-0.3636545600000005</v>
       </c>
       <c r="O77">
-        <v>-0.07074474000000008</v>
+        <v>-0.08000400320000012</v>
       </c>
       <c r="P77">
-        <v>-0.2508222600000003</v>
+        <v>-0.2836505568000004</v>
       </c>
       <c r="Q77">
-        <v>0.8391777399999998</v>
+        <v>0.8063494431999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1673723071063666</v>
+        <v>0.1724378199024652</v>
       </c>
       <c r="T77">
-        <v>2.807674529015393</v>
+        <v>2.924660967724368</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1975880759065149</v>
+        <v>0.1949882328024818</v>
       </c>
       <c r="W77">
-        <v>0.1177940704569236</v>
+        <v>0.1181757274245957</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8981276177568858</v>
+        <v>0.8863101491021899</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1311986296192844</v>
+        <v>0.1322086296192844</v>
       </c>
       <c r="C78">
-        <v>-9.410823308235818</v>
+        <v>-9.823040406544958</v>
       </c>
       <c r="D78">
-        <v>10.73837669176418</v>
+        <v>10.61285959345504</v>
       </c>
       <c r="E78">
-        <v>15.9192</v>
+        <v>16.2059</v>
       </c>
       <c r="F78">
-        <v>21.7892</v>
+        <v>22.0759</v>
       </c>
       <c r="G78">
         <v>1.64</v>
@@ -7665,37 +7665,37 @@
         <v>2.835</v>
       </c>
       <c r="M78">
-        <v>3.19865456</v>
+        <v>3.240742120000001</v>
       </c>
       <c r="N78">
-        <v>-0.3636545600000005</v>
+        <v>-0.4057421200000007</v>
       </c>
       <c r="O78">
-        <v>-0.08000400320000012</v>
+        <v>-0.08926326640000014</v>
       </c>
       <c r="P78">
-        <v>-0.2836505568000004</v>
+        <v>-0.3164788536000005</v>
       </c>
       <c r="Q78">
-        <v>0.8063494431999997</v>
+        <v>0.7735211463999996</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1724378199024652</v>
+        <v>0.1779438120721376</v>
       </c>
       <c r="T78">
-        <v>2.924660967724368</v>
+        <v>3.051820140234123</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1949882328024818</v>
+        <v>0.1924559180907612</v>
       </c>
       <c r="W78">
-        <v>0.1181757274245957</v>
+        <v>0.1185474712242763</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8863101491021899</v>
+        <v>0.8747996276852783</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1322086296192844</v>
+        <v>0.1332186296192844</v>
       </c>
       <c r="C79">
-        <v>-9.823040406544958</v>
+        <v>-10.23235715581307</v>
       </c>
       <c r="D79">
-        <v>10.61285959345504</v>
+        <v>10.49024284418693</v>
       </c>
       <c r="E79">
-        <v>16.2059</v>
+        <v>16.4926</v>
       </c>
       <c r="F79">
-        <v>22.0759</v>
+        <v>22.3626</v>
       </c>
       <c r="G79">
         <v>1.64</v>
@@ -7747,37 +7747,37 @@
         <v>2.835</v>
       </c>
       <c r="M79">
-        <v>3.240742120000001</v>
+        <v>3.28282968</v>
       </c>
       <c r="N79">
-        <v>-0.4057421200000007</v>
+        <v>-0.4478296800000003</v>
       </c>
       <c r="O79">
-        <v>-0.08926326640000014</v>
+        <v>-0.09852252960000007</v>
       </c>
       <c r="P79">
-        <v>-0.3164788536000005</v>
+        <v>-0.3493071504000003</v>
       </c>
       <c r="Q79">
-        <v>0.7735211463999996</v>
+        <v>0.7406928495999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1779438120721376</v>
+        <v>0.1839503489845075</v>
       </c>
       <c r="T79">
-        <v>3.051820140234123</v>
+        <v>3.190539237517493</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1924559180907612</v>
+        <v>0.1899885345254951</v>
       </c>
       <c r="W79">
-        <v>0.1185474712242763</v>
+        <v>0.1189096831316573</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8747996276852783</v>
+        <v>0.8635842478431595</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1332186296192844</v>
+        <v>0.1342286296192844</v>
       </c>
       <c r="C80">
-        <v>-10.23235715581307</v>
+        <v>-10.63887293627065</v>
       </c>
       <c r="D80">
-        <v>10.49024284418693</v>
+        <v>10.37042706372935</v>
       </c>
       <c r="E80">
-        <v>16.4926</v>
+        <v>16.7793</v>
       </c>
       <c r="F80">
-        <v>22.3626</v>
+        <v>22.6493</v>
       </c>
       <c r="G80">
         <v>1.64</v>
@@ -7829,37 +7829,37 @@
         <v>2.835</v>
       </c>
       <c r="M80">
-        <v>3.28282968</v>
+        <v>3.324917240000001</v>
       </c>
       <c r="N80">
-        <v>-0.4478296800000003</v>
+        <v>-0.4899172400000009</v>
       </c>
       <c r="O80">
-        <v>-0.09852252960000007</v>
+        <v>-0.1077817928000002</v>
       </c>
       <c r="P80">
-        <v>-0.3493071504000003</v>
+        <v>-0.3821354472000007</v>
       </c>
       <c r="Q80">
-        <v>0.7406928495999998</v>
+        <v>0.7078645527999994</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1839503489845075</v>
+        <v>0.1905289370313888</v>
       </c>
       <c r="T80">
-        <v>3.190539237517493</v>
+        <v>3.342469677399278</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1899885345254951</v>
+        <v>0.1875836163669445</v>
       </c>
       <c r="W80">
-        <v>0.1189096831316573</v>
+        <v>0.1192627251173326</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8635842478431595</v>
+        <v>0.8526528016679293</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1342286296192844</v>
+        <v>0.1352386296192844</v>
       </c>
       <c r="C81">
-        <v>-10.63887293627065</v>
+        <v>-11.04268263907974</v>
       </c>
       <c r="D81">
-        <v>10.37042706372935</v>
+        <v>10.25331736092026</v>
       </c>
       <c r="E81">
-        <v>16.7793</v>
+        <v>17.066</v>
       </c>
       <c r="F81">
-        <v>22.6493</v>
+        <v>22.936</v>
       </c>
       <c r="G81">
         <v>1.64</v>
@@ -7911,37 +7911,37 @@
         <v>2.835</v>
       </c>
       <c r="M81">
-        <v>3.324917240000001</v>
+        <v>3.367004800000001</v>
       </c>
       <c r="N81">
-        <v>-0.4899172400000009</v>
+        <v>-0.5320048000000011</v>
       </c>
       <c r="O81">
-        <v>-0.1077817928000002</v>
+        <v>-0.1170410560000002</v>
       </c>
       <c r="P81">
-        <v>-0.3821354472000007</v>
+        <v>-0.4149637440000008</v>
       </c>
       <c r="Q81">
-        <v>0.7078645527999994</v>
+        <v>0.6750362559999993</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1905289370313888</v>
+        <v>0.1977653838829582</v>
       </c>
       <c r="T81">
-        <v>3.342469677399278</v>
+        <v>3.509593161269242</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1875836163669445</v>
+        <v>0.1852388211623577</v>
       </c>
       <c r="W81">
-        <v>0.1192627251173326</v>
+        <v>0.1196069410533659</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8526528016679293</v>
+        <v>0.8419946416470803</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1352386296192844</v>
+        <v>0.1362486296192844</v>
       </c>
       <c r="C82">
-        <v>-11.04268263907974</v>
+        <v>-11.44387691697117</v>
       </c>
       <c r="D82">
-        <v>10.25331736092026</v>
+        <v>10.13882308302883</v>
       </c>
       <c r="E82">
-        <v>17.066</v>
+        <v>17.3527</v>
       </c>
       <c r="F82">
-        <v>22.936</v>
+        <v>23.2227</v>
       </c>
       <c r="G82">
         <v>1.64</v>
@@ -7993,37 +7993,37 @@
         <v>2.835</v>
       </c>
       <c r="M82">
-        <v>3.367004800000001</v>
+        <v>3.409092360000001</v>
       </c>
       <c r="N82">
-        <v>-0.5320048000000011</v>
+        <v>-0.5740923600000007</v>
       </c>
       <c r="O82">
-        <v>-0.1170410560000002</v>
+        <v>-0.1263003192000002</v>
       </c>
       <c r="P82">
-        <v>-0.4149637440000008</v>
+        <v>-0.4477920408000006</v>
       </c>
       <c r="Q82">
-        <v>0.6750362559999993</v>
+        <v>0.6422079591999995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1977653838829582</v>
+        <v>0.2057635619820613</v>
       </c>
       <c r="T82">
-        <v>3.509593161269242</v>
+        <v>3.694308590809729</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1852388211623577</v>
+        <v>0.1829519221356619</v>
       </c>
       <c r="W82">
-        <v>0.1196069410533659</v>
+        <v>0.1199426578304848</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8419946416470803</v>
+        <v>0.8315996460711904</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1362486296192844</v>
+        <v>0.1372586296192844</v>
       </c>
       <c r="C83">
-        <v>-11.44387691697117</v>
+        <v>-11.84254241827472</v>
       </c>
       <c r="D83">
-        <v>10.13882308302883</v>
+        <v>10.02685758172528</v>
       </c>
       <c r="E83">
-        <v>17.3527</v>
+        <v>17.6394</v>
       </c>
       <c r="F83">
-        <v>23.2227</v>
+        <v>23.5094</v>
       </c>
       <c r="G83">
         <v>1.64</v>
@@ -8075,37 +8075,37 @@
         <v>2.835</v>
       </c>
       <c r="M83">
-        <v>3.409092360000001</v>
+        <v>3.451179920000001</v>
       </c>
       <c r="N83">
-        <v>-0.5740923600000007</v>
+        <v>-0.6161799200000009</v>
       </c>
       <c r="O83">
-        <v>-0.1263003192000002</v>
+        <v>-0.1355595824000002</v>
       </c>
       <c r="P83">
-        <v>-0.4477920408000006</v>
+        <v>-0.4806203376000007</v>
       </c>
       <c r="Q83">
-        <v>0.6422079591999995</v>
+        <v>0.6093796623999994</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2057635619820613</v>
+        <v>0.2146504265366203</v>
       </c>
       <c r="T83">
-        <v>3.694308590809729</v>
+        <v>3.899547956965825</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1829519221356619</v>
+        <v>0.1807208011340075</v>
       </c>
       <c r="W83">
-        <v>0.1199426578304848</v>
+        <v>0.1202701863935277</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8315996460711904</v>
+        <v>0.8214581869727613</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1372586296192844</v>
+        <v>0.1382686296192844</v>
       </c>
       <c r="C84">
-        <v>-11.84254241827472</v>
+        <v>-12.23876200561195</v>
       </c>
       <c r="D84">
-        <v>10.02685758172528</v>
+        <v>9.917337994388053</v>
       </c>
       <c r="E84">
-        <v>17.6394</v>
+        <v>17.9261</v>
       </c>
       <c r="F84">
-        <v>23.5094</v>
+        <v>23.7961</v>
       </c>
       <c r="G84">
         <v>1.64</v>
@@ -8157,37 +8157,37 @@
         <v>2.835</v>
       </c>
       <c r="M84">
-        <v>3.451179920000001</v>
+        <v>3.493267480000001</v>
       </c>
       <c r="N84">
-        <v>-0.6161799200000009</v>
+        <v>-0.6582674800000006</v>
       </c>
       <c r="O84">
-        <v>-0.1355595824000002</v>
+        <v>-0.1448188456000001</v>
       </c>
       <c r="P84">
-        <v>-0.4806203376000007</v>
+        <v>-0.5134486344000004</v>
       </c>
       <c r="Q84">
-        <v>0.6093796623999994</v>
+        <v>0.5765513655999996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2146504265366203</v>
+        <v>0.2245828045681862</v>
       </c>
       <c r="T84">
-        <v>3.899547956965825</v>
+        <v>4.128933130904992</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1807208011340075</v>
+        <v>0.1785434420842002</v>
       </c>
       <c r="W84">
-        <v>0.1202701863935277</v>
+        <v>0.1205898227020394</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8214581869727613</v>
+        <v>0.8115611003827281</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1382686296192844</v>
+        <v>0.1392786296192844</v>
       </c>
       <c r="C85">
-        <v>-12.23876200561195</v>
+        <v>-12.63261496041164</v>
       </c>
       <c r="D85">
-        <v>9.917337994388053</v>
+        <v>9.810185039588365</v>
       </c>
       <c r="E85">
-        <v>17.9261</v>
+        <v>18.2128</v>
       </c>
       <c r="F85">
-        <v>23.7961</v>
+        <v>24.0828</v>
       </c>
       <c r="G85">
         <v>1.64</v>
@@ -8239,37 +8239,37 @@
         <v>2.835</v>
       </c>
       <c r="M85">
-        <v>3.493267480000001</v>
+        <v>3.535355040000001</v>
       </c>
       <c r="N85">
-        <v>-0.6582674800000006</v>
+        <v>-0.7003550400000007</v>
       </c>
       <c r="O85">
-        <v>-0.1448188456000001</v>
+        <v>-0.1540781088000002</v>
       </c>
       <c r="P85">
-        <v>-0.5134486344000004</v>
+        <v>-0.5462769312000005</v>
       </c>
       <c r="Q85">
-        <v>0.5765513655999996</v>
+        <v>0.5437230687999995</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2245828045681862</v>
+        <v>0.2357567298536979</v>
       </c>
       <c r="T85">
-        <v>4.128933130904992</v>
+        <v>4.386991451586555</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1785434420842002</v>
+        <v>0.1764179249165311</v>
       </c>
       <c r="W85">
-        <v>0.1205898227020394</v>
+        <v>0.1209018486222533</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8115611003827281</v>
+        <v>0.801899658711505</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1392786296192843</v>
+        <v>0.1876105802514416</v>
       </c>
       <c r="C86">
-        <v>-12.63261496041163</v>
+        <v>-16.26282697612312</v>
       </c>
       <c r="D86">
-        <v>9.810185039588372</v>
+        <v>6.466673023876884</v>
       </c>
       <c r="E86">
-        <v>18.2128</v>
+        <v>18.4995</v>
       </c>
       <c r="F86">
-        <v>24.0828</v>
+        <v>24.3695</v>
       </c>
       <c r="G86">
         <v>1.64</v>
@@ -8321,45 +8321,45 @@
         <v>2.835</v>
       </c>
       <c r="M86">
-        <v>3.53535504</v>
+        <v>4.893395600000001</v>
       </c>
       <c r="N86">
-        <v>-0.7003550400000003</v>
+        <v>-2.058395600000001</v>
       </c>
       <c r="O86">
-        <v>-0.1540781088000001</v>
+        <v>-0.4528470320000001</v>
       </c>
       <c r="P86">
-        <v>-0.5462769312000002</v>
+        <v>-1.605548568000001</v>
       </c>
       <c r="Q86">
-        <v>0.5437230687999999</v>
+        <v>-0.5155485680000005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2357567298536977</v>
+        <v>0.2579001827249926</v>
       </c>
       <c r="T86">
-        <v>4.386991451586551</v>
+        <v>4.898387591801215</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1764179249165311</v>
+        <v>0.1274575061946759</v>
       </c>
       <c r="W86">
-        <v>0.1209018486222532</v>
+        <v>0.1752065327561091</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8018996587115053</v>
+        <v>0.5793523008848905</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1876105802514416</v>
+        <v>0.1891605802514416</v>
       </c>
       <c r="C87">
-        <v>-16.26282697612312</v>
+        <v>-16.61944398656929</v>
       </c>
       <c r="D87">
-        <v>6.466673023876884</v>
+        <v>6.396756013430714</v>
       </c>
       <c r="E87">
-        <v>18.4995</v>
+        <v>18.7862</v>
       </c>
       <c r="F87">
-        <v>24.3695</v>
+        <v>24.6562</v>
       </c>
       <c r="G87">
         <v>1.64</v>
@@ -8403,37 +8403,37 @@
         <v>2.835</v>
       </c>
       <c r="M87">
-        <v>4.893395600000001</v>
+        <v>4.95096496</v>
       </c>
       <c r="N87">
-        <v>-2.058395600000001</v>
+        <v>-2.11596496</v>
       </c>
       <c r="O87">
-        <v>-0.4528470320000001</v>
+        <v>-0.4655122912000001</v>
       </c>
       <c r="P87">
-        <v>-1.605548568000001</v>
+        <v>-1.6504526688</v>
       </c>
       <c r="Q87">
-        <v>-0.5155485680000005</v>
+        <v>-0.5604526688000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2579001827249926</v>
+        <v>0.2730501957767777</v>
       </c>
       <c r="T87">
-        <v>4.898387591801215</v>
+        <v>5.248272419787015</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1274575061946759</v>
+        <v>0.1259754421691565</v>
       </c>
       <c r="W87">
-        <v>0.1752065327561091</v>
+        <v>0.1755041312124334</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5793523008848905</v>
+        <v>0.5726156462234384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1891605802514416</v>
+        <v>0.1907105802514416</v>
       </c>
       <c r="C88">
-        <v>-16.61944398656929</v>
+        <v>-16.97456529717072</v>
       </c>
       <c r="D88">
-        <v>6.396756013430714</v>
+        <v>6.32833470282928</v>
       </c>
       <c r="E88">
-        <v>18.7862</v>
+        <v>19.0729</v>
       </c>
       <c r="F88">
-        <v>24.6562</v>
+        <v>24.9429</v>
       </c>
       <c r="G88">
         <v>1.64</v>
@@ -8485,37 +8485,37 @@
         <v>2.835</v>
       </c>
       <c r="M88">
-        <v>4.95096496</v>
+        <v>5.008534320000001</v>
       </c>
       <c r="N88">
-        <v>-2.11596496</v>
+        <v>-2.173534320000001</v>
       </c>
       <c r="O88">
-        <v>-0.4655122912000001</v>
+        <v>-0.4781775504000002</v>
       </c>
       <c r="P88">
-        <v>-1.6504526688</v>
+        <v>-1.695356769600001</v>
       </c>
       <c r="Q88">
-        <v>-0.5604526688000002</v>
+        <v>-0.6053567696000006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2730501957767777</v>
+        <v>0.2905309800672992</v>
       </c>
       <c r="T88">
-        <v>5.248272419787015</v>
+        <v>5.651985682847555</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1259754421691565</v>
+        <v>0.1245274485810052</v>
       </c>
       <c r="W88">
-        <v>0.1755041312124334</v>
+        <v>0.1757948883249342</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5726156462234384</v>
+        <v>0.5660338571863873</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1907105802514416</v>
+        <v>0.1922605802514416</v>
       </c>
       <c r="C89">
-        <v>-16.97456529717072</v>
+        <v>-17.32823839513705</v>
       </c>
       <c r="D89">
-        <v>6.32833470282928</v>
+        <v>6.261361604862953</v>
       </c>
       <c r="E89">
-        <v>19.0729</v>
+        <v>19.3596</v>
       </c>
       <c r="F89">
-        <v>24.9429</v>
+        <v>25.2296</v>
       </c>
       <c r="G89">
         <v>1.64</v>
@@ -8567,37 +8567,37 @@
         <v>2.835</v>
       </c>
       <c r="M89">
-        <v>5.008534320000001</v>
+        <v>5.06610368</v>
       </c>
       <c r="N89">
-        <v>-2.173534320000001</v>
+        <v>-2.23110368</v>
       </c>
       <c r="O89">
-        <v>-0.4781775504000002</v>
+        <v>-0.4908428096000001</v>
       </c>
       <c r="P89">
-        <v>-1.695356769600001</v>
+        <v>-1.7402608704</v>
       </c>
       <c r="Q89">
-        <v>-0.6053567696000006</v>
+        <v>-0.6502608704000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2905309800672992</v>
+        <v>0.3109252284062408</v>
       </c>
       <c r="T89">
-        <v>5.651985682847555</v>
+        <v>6.122984489751519</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1245274485810052</v>
+        <v>0.1231123639380393</v>
       </c>
       <c r="W89">
-        <v>0.1757948883249342</v>
+        <v>0.1760790373212417</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5660338571863873</v>
+        <v>0.5596016542638148</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1922605802514416</v>
+        <v>0.1938105802514416</v>
       </c>
       <c r="C90">
-        <v>-17.32823839513705</v>
+        <v>-17.68050877849107</v>
       </c>
       <c r="D90">
-        <v>6.261361604862953</v>
+        <v>6.195791221508933</v>
       </c>
       <c r="E90">
-        <v>19.3596</v>
+        <v>19.6463</v>
       </c>
       <c r="F90">
-        <v>25.2296</v>
+        <v>25.5163</v>
       </c>
       <c r="G90">
         <v>1.64</v>
@@ -8649,37 +8649,37 @@
         <v>2.835</v>
       </c>
       <c r="M90">
-        <v>5.06610368</v>
+        <v>5.123673040000001</v>
       </c>
       <c r="N90">
-        <v>-2.23110368</v>
+        <v>-2.288673040000001</v>
       </c>
       <c r="O90">
-        <v>-0.4908428096000001</v>
+        <v>-0.5035080688000002</v>
       </c>
       <c r="P90">
-        <v>-1.7402608704</v>
+        <v>-1.785164971200001</v>
       </c>
       <c r="Q90">
-        <v>-0.6502608704000001</v>
+        <v>-0.6951649712000005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3109252284062408</v>
+        <v>0.3350275218977172</v>
       </c>
       <c r="T90">
-        <v>6.122984489751519</v>
+        <v>6.679619443365293</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1231123639380393</v>
+        <v>0.1217290789499714</v>
       </c>
       <c r="W90">
-        <v>0.1760790373212417</v>
+        <v>0.1763568009468457</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5596016542638148</v>
+        <v>0.5533139952271426</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1938105802514416</v>
+        <v>0.1953605802514416</v>
       </c>
       <c r="C91">
-        <v>-17.68050877849107</v>
+        <v>-18.03142005914533</v>
       </c>
       <c r="D91">
-        <v>6.195791221508933</v>
+        <v>6.131579940854675</v>
       </c>
       <c r="E91">
-        <v>19.6463</v>
+        <v>19.933</v>
       </c>
       <c r="F91">
-        <v>25.5163</v>
+        <v>25.803</v>
       </c>
       <c r="G91">
         <v>1.64</v>
@@ -8731,37 +8731,37 @@
         <v>2.835</v>
       </c>
       <c r="M91">
-        <v>5.123673040000001</v>
+        <v>5.1812424</v>
       </c>
       <c r="N91">
-        <v>-2.288673040000001</v>
+        <v>-2.3462424</v>
       </c>
       <c r="O91">
-        <v>-0.5035080688000002</v>
+        <v>-0.516173328</v>
       </c>
       <c r="P91">
-        <v>-1.785164971200001</v>
+        <v>-1.830069072</v>
       </c>
       <c r="Q91">
-        <v>-0.6951649712000005</v>
+        <v>-0.7400690720000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3350275218977172</v>
+        <v>0.363950274087489</v>
       </c>
       <c r="T91">
-        <v>6.679619443365293</v>
+        <v>7.347581387701823</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1217290789499714</v>
+        <v>0.1203765336283051</v>
       </c>
       <c r="W91">
-        <v>0.1763568009468457</v>
+        <v>0.1766283920474364</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5533139952271426</v>
+        <v>0.5471660619468411</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1953605802514416</v>
+        <v>0.1969105802514416</v>
       </c>
       <c r="C92">
-        <v>-18.03142005914533</v>
+        <v>-18.38101405963497</v>
       </c>
       <c r="D92">
-        <v>6.131579940854675</v>
+        <v>6.068685940365033</v>
       </c>
       <c r="E92">
-        <v>19.933</v>
+        <v>20.2197</v>
       </c>
       <c r="F92">
-        <v>25.803</v>
+        <v>26.0897</v>
       </c>
       <c r="G92">
         <v>1.64</v>
@@ -8813,37 +8813,37 @@
         <v>2.835</v>
       </c>
       <c r="M92">
-        <v>5.1812424</v>
+        <v>5.238811760000001</v>
       </c>
       <c r="N92">
-        <v>-2.3462424</v>
+        <v>-2.403811760000001</v>
       </c>
       <c r="O92">
-        <v>-0.516173328</v>
+        <v>-0.5288385872000002</v>
       </c>
       <c r="P92">
-        <v>-1.830069072</v>
+        <v>-1.874973172800001</v>
       </c>
       <c r="Q92">
-        <v>-0.7400690720000003</v>
+        <v>-0.7849731728000007</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.363950274087489</v>
+        <v>0.3993003045416545</v>
       </c>
       <c r="T92">
-        <v>7.347581387701823</v>
+        <v>8.163979319668695</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1203765336283051</v>
+        <v>0.1190537145774445</v>
       </c>
       <c r="W92">
-        <v>0.1766283920474364</v>
+        <v>0.1768940141128491</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5471660619468411</v>
+        <v>0.5411532480792933</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1969105802514416</v>
+        <v>0.1984605802514416</v>
       </c>
       <c r="C93">
-        <v>-18.38101405963497</v>
+        <v>-18.72933090395767</v>
       </c>
       <c r="D93">
-        <v>6.068685940365033</v>
+        <v>6.007069096042334</v>
       </c>
       <c r="E93">
-        <v>20.2197</v>
+        <v>20.5064</v>
       </c>
       <c r="F93">
-        <v>26.0897</v>
+        <v>26.3764</v>
       </c>
       <c r="G93">
         <v>1.64</v>
@@ -8895,37 +8895,37 @@
         <v>2.835</v>
       </c>
       <c r="M93">
-        <v>5.238811760000001</v>
+        <v>5.296381120000001</v>
       </c>
       <c r="N93">
-        <v>-2.403811760000001</v>
+        <v>-2.461381120000001</v>
       </c>
       <c r="O93">
-        <v>-0.5288385872000002</v>
+        <v>-0.5415038464000003</v>
       </c>
       <c r="P93">
-        <v>-1.874973172800001</v>
+        <v>-1.919877273600001</v>
       </c>
       <c r="Q93">
-        <v>-0.7849731728000007</v>
+        <v>-0.8298772736000009</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3993003045416545</v>
+        <v>0.4434878426093614</v>
       </c>
       <c r="T93">
-        <v>8.163979319668695</v>
+        <v>9.184476734627284</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1190537145774445</v>
+        <v>0.1177596524624723</v>
       </c>
       <c r="W93">
-        <v>0.1768940141128491</v>
+        <v>0.1771538617855355</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5411532480792933</v>
+        <v>0.5352711475566923</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1984605802514416</v>
+        <v>0.2000105802514416</v>
       </c>
       <c r="C94">
-        <v>-18.72933090395767</v>
+        <v>-19.07640910293522</v>
       </c>
       <c r="D94">
-        <v>6.007069096042334</v>
+        <v>5.946690897064779</v>
       </c>
       <c r="E94">
-        <v>20.5064</v>
+        <v>20.7931</v>
       </c>
       <c r="F94">
-        <v>26.3764</v>
+        <v>26.6631</v>
       </c>
       <c r="G94">
         <v>1.64</v>
@@ -8977,37 +8977,37 @@
         <v>2.835</v>
       </c>
       <c r="M94">
-        <v>5.296381120000001</v>
+        <v>5.353950480000001</v>
       </c>
       <c r="N94">
-        <v>-2.461381120000001</v>
+        <v>-2.518950480000001</v>
       </c>
       <c r="O94">
-        <v>-0.5415038464000003</v>
+        <v>-0.5541691056000002</v>
       </c>
       <c r="P94">
-        <v>-1.919877273600001</v>
+        <v>-1.964781374400001</v>
       </c>
       <c r="Q94">
-        <v>-0.8298772736000009</v>
+        <v>-0.8747813744000006</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4434878426093614</v>
+        <v>0.5003003915535559</v>
       </c>
       <c r="T94">
-        <v>9.184476734627284</v>
+        <v>10.49654483957404</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1177596524624723</v>
+        <v>0.1164934196402952</v>
       </c>
       <c r="W94">
-        <v>0.1771538617855355</v>
+        <v>0.1774081213362287</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5352711475566923</v>
+        <v>0.5295155438195236</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2000105802514416</v>
+        <v>0.2015605802514416</v>
       </c>
       <c r="C95">
-        <v>-19.07640910293522</v>
+        <v>-19.42228563447851</v>
       </c>
       <c r="D95">
-        <v>5.946690897064779</v>
+        <v>5.88751436552149</v>
       </c>
       <c r="E95">
-        <v>20.7931</v>
+        <v>21.0798</v>
       </c>
       <c r="F95">
-        <v>26.6631</v>
+        <v>26.9498</v>
       </c>
       <c r="G95">
         <v>1.64</v>
@@ -9059,37 +9059,37 @@
         <v>2.835</v>
       </c>
       <c r="M95">
-        <v>5.353950480000001</v>
+        <v>5.41151984</v>
       </c>
       <c r="N95">
-        <v>-2.518950480000001</v>
+        <v>-2.57651984</v>
       </c>
       <c r="O95">
-        <v>-0.5541691056000002</v>
+        <v>-0.5668343648000002</v>
       </c>
       <c r="P95">
-        <v>-1.964781374400001</v>
+        <v>-2.0096854752</v>
       </c>
       <c r="Q95">
-        <v>-0.8747813744000006</v>
+        <v>-0.9196854752000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5003003915535559</v>
+        <v>0.576050456812482</v>
       </c>
       <c r="T95">
-        <v>10.49654483957404</v>
+        <v>12.24596897950305</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1164934196402952</v>
+        <v>0.1152541279419942</v>
       </c>
       <c r="W95">
-        <v>0.1774081213362287</v>
+        <v>0.1776569711092476</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5295155438195236</v>
+        <v>0.5238823997363373</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2015605802514416</v>
+        <v>0.2031105802514416</v>
       </c>
       <c r="C96">
-        <v>-19.42228563447851</v>
+        <v>-19.76699601910726</v>
       </c>
       <c r="D96">
-        <v>5.88751436552149</v>
+        <v>5.829503980892739</v>
       </c>
       <c r="E96">
-        <v>21.0798</v>
+        <v>21.3665</v>
       </c>
       <c r="F96">
-        <v>26.9498</v>
+        <v>27.2365</v>
       </c>
       <c r="G96">
         <v>1.64</v>
@@ -9141,37 +9141,37 @@
         <v>2.835</v>
       </c>
       <c r="M96">
-        <v>5.41151984</v>
+        <v>5.469089200000001</v>
       </c>
       <c r="N96">
-        <v>-2.57651984</v>
+        <v>-2.634089200000001</v>
       </c>
       <c r="O96">
-        <v>-0.5668343648000002</v>
+        <v>-0.5794996240000002</v>
       </c>
       <c r="P96">
-        <v>-2.0096854752</v>
+        <v>-2.054589576000001</v>
       </c>
       <c r="Q96">
-        <v>-0.9196854752000003</v>
+        <v>-0.9645895760000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.576050456812482</v>
+        <v>0.6821005481749787</v>
       </c>
       <c r="T96">
-        <v>12.24596897950305</v>
+        <v>14.69516277540366</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1152541279419942</v>
+        <v>0.1140409265952363</v>
       </c>
       <c r="W96">
-        <v>0.1776569711092476</v>
+        <v>0.1779005819396766</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5238823997363373</v>
+        <v>0.5183678481601652</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2031105802514416</v>
+        <v>0.2046605802514416</v>
       </c>
       <c r="C97">
-        <v>-19.76699601910726</v>
+        <v>-20.11057439104876</v>
       </c>
       <c r="D97">
-        <v>5.829503980892739</v>
+        <v>5.772625608951242</v>
       </c>
       <c r="E97">
-        <v>21.3665</v>
+        <v>21.6532</v>
       </c>
       <c r="F97">
-        <v>27.2365</v>
+        <v>27.5232</v>
       </c>
       <c r="G97">
         <v>1.64</v>
@@ -9223,37 +9223,37 @@
         <v>2.835</v>
       </c>
       <c r="M97">
-        <v>5.469089200000001</v>
+        <v>5.52665856</v>
       </c>
       <c r="N97">
-        <v>-2.634089200000001</v>
+        <v>-2.69165856</v>
       </c>
       <c r="O97">
-        <v>-0.5794996240000002</v>
+        <v>-0.5921648832000002</v>
       </c>
       <c r="P97">
-        <v>-2.054589576000001</v>
+        <v>-2.0994936768</v>
       </c>
       <c r="Q97">
-        <v>-0.9645895760000005</v>
+        <v>-1.0094936768</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6821005481749787</v>
+        <v>0.8411756852187239</v>
       </c>
       <c r="T97">
-        <v>14.69516277540366</v>
+        <v>18.36895346925459</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1140409265952363</v>
+        <v>0.112853000276536</v>
       </c>
       <c r="W97">
-        <v>0.1779005819396766</v>
+        <v>0.1781391175444716</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5183678481601652</v>
+        <v>0.5129681830751636</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2046605802514416</v>
+        <v>0.2062105802514416</v>
       </c>
       <c r="C98">
-        <v>-20.11057439104876</v>
+        <v>-20.45305356521451</v>
       </c>
       <c r="D98">
-        <v>5.772625608951242</v>
+        <v>5.716846434785491</v>
       </c>
       <c r="E98">
-        <v>21.6532</v>
+        <v>21.9399</v>
       </c>
       <c r="F98">
-        <v>27.5232</v>
+        <v>27.8099</v>
       </c>
       <c r="G98">
         <v>1.64</v>
@@ -9305,37 +9305,37 @@
         <v>2.835</v>
       </c>
       <c r="M98">
-        <v>5.52665856</v>
+        <v>5.584227920000001</v>
       </c>
       <c r="N98">
-        <v>-2.69165856</v>
+        <v>-2.749227920000001</v>
       </c>
       <c r="O98">
-        <v>-0.5921648832000002</v>
+        <v>-0.6048301424000002</v>
       </c>
       <c r="P98">
-        <v>-2.0994936768</v>
+        <v>-2.144397777600001</v>
       </c>
       <c r="Q98">
-        <v>-1.0094936768</v>
+        <v>-1.054397777600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8411756852187218</v>
+        <v>1.106300913624962</v>
       </c>
       <c r="T98">
-        <v>18.36895346925454</v>
+        <v>24.49193795900606</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.112853000276536</v>
+        <v>0.1116895672839944</v>
       </c>
       <c r="W98">
-        <v>0.1781391175444716</v>
+        <v>0.1783727348893739</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5129681830751636</v>
+        <v>0.5076798512908834</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2062105802514416</v>
+        <v>0.2077605802514416</v>
       </c>
       <c r="C99">
-        <v>-20.45305356521451</v>
+        <v>-20.79446510033102</v>
       </c>
       <c r="D99">
-        <v>5.716846434785491</v>
+        <v>5.662134899668978</v>
       </c>
       <c r="E99">
-        <v>21.9399</v>
+        <v>22.2266</v>
       </c>
       <c r="F99">
-        <v>27.8099</v>
+        <v>28.0966</v>
       </c>
       <c r="G99">
         <v>1.64</v>
@@ -9387,37 +9387,37 @@
         <v>2.835</v>
       </c>
       <c r="M99">
-        <v>5.584227920000001</v>
+        <v>5.64179728</v>
       </c>
       <c r="N99">
-        <v>-2.749227920000001</v>
+        <v>-2.806797280000001</v>
       </c>
       <c r="O99">
-        <v>-0.6048301424000002</v>
+        <v>-0.6174954016000002</v>
       </c>
       <c r="P99">
-        <v>-2.144397777600001</v>
+        <v>-2.1893018784</v>
       </c>
       <c r="Q99">
-        <v>-1.054397777600001</v>
+        <v>-1.0993018784</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.106300913624962</v>
+        <v>1.636551370437444</v>
       </c>
       <c r="T99">
-        <v>24.49193795900606</v>
+        <v>36.73790693850908</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1116895672839944</v>
+        <v>0.1105498778219128</v>
       </c>
       <c r="W99">
-        <v>0.1783727348893739</v>
+        <v>0.1786015845333599</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5076798512908834</v>
+        <v>0.5024994446450581</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2077605802514416</v>
+        <v>0.244534354506776</v>
       </c>
       <c r="C100">
-        <v>-20.79446510033102</v>
+        <v>-22.12888566741888</v>
       </c>
       <c r="D100">
-        <v>5.662134899668978</v>
+        <v>4.614414332581125</v>
       </c>
       <c r="E100">
-        <v>22.2266</v>
+        <v>22.5133</v>
       </c>
       <c r="F100">
-        <v>28.0966</v>
+        <v>28.3833</v>
       </c>
       <c r="G100">
         <v>1.64</v>
@@ -9469,129 +9469,47 @@
         <v>2.835</v>
       </c>
       <c r="M100">
-        <v>5.64179728</v>
+        <v>6.692782140000001</v>
       </c>
       <c r="N100">
-        <v>-2.806797280000001</v>
+        <v>-3.857782140000001</v>
       </c>
       <c r="O100">
-        <v>-0.6174954016000002</v>
+        <v>-0.8487120708000002</v>
       </c>
       <c r="P100">
-        <v>-2.1893018784</v>
+        <v>-3.009070069200001</v>
       </c>
       <c r="Q100">
-        <v>-1.0993018784</v>
+        <v>-1.919070069200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.636551370437444</v>
+        <v>3.284680166408327</v>
       </c>
       <c r="T100">
-        <v>36.73790693850908</v>
+        <v>74.80092763067729</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1105498778219128</v>
+        <v>0.09318994507118379</v>
       </c>
       <c r="W100">
-        <v>0.1786015845333599</v>
+        <v>0.2138258109522149</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5024994446450581</v>
+        <v>0.4235906594144717</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.244534354506776</v>
-      </c>
-      <c r="C101">
-        <v>-22.12888566741888</v>
-      </c>
-      <c r="D101">
-        <v>4.614414332581125</v>
-      </c>
-      <c r="E101">
-        <v>22.5133</v>
-      </c>
-      <c r="F101">
-        <v>28.3833</v>
-      </c>
-      <c r="G101">
-        <v>1.64</v>
-      </c>
-      <c r="H101">
-        <v>22.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.925</v>
-      </c>
-      <c r="K101">
-        <v>1.09</v>
-      </c>
-      <c r="L101">
-        <v>2.835</v>
-      </c>
-      <c r="M101">
-        <v>6.692782140000001</v>
-      </c>
-      <c r="N101">
-        <v>-3.857782140000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.8487120708000002</v>
-      </c>
-      <c r="P101">
-        <v>-3.009070069200001</v>
-      </c>
-      <c r="Q101">
-        <v>-1.919070069200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.284680166408327</v>
-      </c>
-      <c r="T101">
-        <v>74.80092763067729</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09318994507118379</v>
-      </c>
-      <c r="W101">
-        <v>0.2138258109522149</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4235906594144717</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
